--- a/research/traditional_assets/database/data/chile/chile_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_business_consumer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0978608650872024</v>
+        <v>0.09762949075146697</v>
       </c>
       <c r="C2">
-        <v>30.4512647843133</v>
+        <v>30.25813779190401</v>
       </c>
       <c r="D2">
-        <v>28.8012647843133</v>
+        <v>28.92983779190401</v>
       </c>
       <c r="E2">
-        <v>-8.17</v>
+        <v>-7.8483</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3217</v>
       </c>
       <c r="G2">
         <v>1.65</v>
@@ -1451,28 +1451,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01618151</v>
       </c>
       <c r="N2">
-        <v>8.194489795918368</v>
+        <v>8.178308285918369</v>
       </c>
       <c r="O2">
-        <v>2.21251224489796</v>
+        <v>2.20814323719796</v>
       </c>
       <c r="P2">
-        <v>5.981977551020409</v>
+        <v>5.97016504872041</v>
       </c>
       <c r="Q2">
-        <v>9.011977551020408</v>
+        <v>9.00016504872041</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0978608650872024</v>
+        <v>0.09824474823380502</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9605439817369686</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>506.4106993672636</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09762949075146697</v>
+        <v>0.09739811641573154</v>
       </c>
       <c r="C3">
-        <v>30.25813779190401</v>
+        <v>30.06616388399823</v>
       </c>
       <c r="D3">
-        <v>28.92983779190401</v>
+        <v>29.05956388399823</v>
       </c>
       <c r="E3">
-        <v>-7.8483</v>
+        <v>-7.5266</v>
       </c>
       <c r="F3">
-        <v>0.3217</v>
+        <v>0.6434000000000001</v>
       </c>
       <c r="G3">
         <v>1.65</v>
@@ -1533,28 +1533,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M3">
-        <v>0.01618151</v>
+        <v>0.03236302</v>
       </c>
       <c r="N3">
-        <v>8.178308285918369</v>
+        <v>8.162126775918368</v>
       </c>
       <c r="O3">
-        <v>2.20814323719796</v>
+        <v>2.203774229497959</v>
       </c>
       <c r="P3">
-        <v>5.97016504872041</v>
+        <v>5.958352546420409</v>
       </c>
       <c r="Q3">
-        <v>9.00016504872041</v>
+        <v>8.988352546420408</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09824474823380502</v>
+        <v>0.0986364657303383</v>
       </c>
       <c r="T3">
-        <v>0.9605439817369686</v>
+        <v>0.9677184252514781</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>506.4106993672636</v>
+        <v>253.2053496836318</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09739811641573154</v>
+        <v>0.09716674207999607</v>
       </c>
       <c r="C4">
-        <v>30.06616388399823</v>
+        <v>29.87535864232165</v>
       </c>
       <c r="D4">
-        <v>29.05956388399823</v>
+        <v>29.19045864232165</v>
       </c>
       <c r="E4">
-        <v>-7.5266</v>
+        <v>-7.2049</v>
       </c>
       <c r="F4">
-        <v>0.6434000000000001</v>
+        <v>0.9651000000000001</v>
       </c>
       <c r="G4">
         <v>1.65</v>
@@ -1615,28 +1615,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M4">
-        <v>0.03236302</v>
+        <v>0.04854453</v>
       </c>
       <c r="N4">
-        <v>8.162126775918368</v>
+        <v>8.145945265918369</v>
       </c>
       <c r="O4">
-        <v>2.203774229497959</v>
+        <v>2.19940522179796</v>
       </c>
       <c r="P4">
-        <v>5.958352546420409</v>
+        <v>5.946540044120409</v>
       </c>
       <c r="Q4">
-        <v>8.988352546420408</v>
+        <v>8.976540044120409</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0986364657303383</v>
+        <v>0.09903625987628462</v>
       </c>
       <c r="T4">
-        <v>0.9677184252514781</v>
+        <v>0.9750407954363898</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>253.2053496836318</v>
+        <v>168.8035664557545</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09716674207999607</v>
+        <v>0.09693536774426062</v>
       </c>
       <c r="C5">
-        <v>29.87535864232165</v>
+        <v>29.68573793061304</v>
       </c>
       <c r="D5">
-        <v>29.19045864232165</v>
+        <v>29.32253793061304</v>
       </c>
       <c r="E5">
-        <v>-7.2049</v>
+        <v>-6.8832</v>
       </c>
       <c r="F5">
-        <v>0.9651000000000001</v>
+        <v>1.2868</v>
       </c>
       <c r="G5">
         <v>1.65</v>
@@ -1697,28 +1697,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M5">
-        <v>0.04854453</v>
+        <v>0.06472604</v>
       </c>
       <c r="N5">
-        <v>8.145945265918369</v>
+        <v>8.129763755918368</v>
       </c>
       <c r="O5">
-        <v>2.19940522179796</v>
+        <v>2.19503621409796</v>
       </c>
       <c r="P5">
-        <v>5.946540044120409</v>
+        <v>5.934727541820409</v>
       </c>
       <c r="Q5">
-        <v>8.976540044120409</v>
+        <v>8.964727541820409</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09903625987628462</v>
+        <v>0.09944438306693815</v>
       </c>
       <c r="T5">
-        <v>0.9750407954363898</v>
+        <v>0.9825157150001539</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>168.8035664557545</v>
+        <v>126.6026748418159</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09693536774426062</v>
+        <v>0.09670399340852517</v>
       </c>
       <c r="C6">
-        <v>29.68573793061304</v>
+        <v>29.49731790103353</v>
       </c>
       <c r="D6">
-        <v>29.32253793061304</v>
+        <v>29.45581790103353</v>
       </c>
       <c r="E6">
-        <v>-6.8832</v>
+        <v>-6.5615</v>
       </c>
       <c r="F6">
-        <v>1.2868</v>
+        <v>1.6085</v>
       </c>
       <c r="G6">
         <v>1.65</v>
@@ -1779,28 +1779,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M6">
-        <v>0.06472604</v>
+        <v>0.08090755000000001</v>
       </c>
       <c r="N6">
-        <v>8.129763755918368</v>
+        <v>8.113582245918369</v>
       </c>
       <c r="O6">
-        <v>2.19503621409796</v>
+        <v>2.19066720639796</v>
       </c>
       <c r="P6">
-        <v>5.934727541820409</v>
+        <v>5.92291503952041</v>
       </c>
       <c r="Q6">
-        <v>8.964727541820409</v>
+        <v>8.952915039520409</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09944438306693815</v>
+        <v>0.09986109832476334</v>
       </c>
       <c r="T6">
-        <v>0.9825157150001539</v>
+        <v>0.990148001291576</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>126.6026748418159</v>
+        <v>101.2821398734527</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09670399340852517</v>
+        <v>0.09647261907278974</v>
       </c>
       <c r="C7">
-        <v>29.49731790103353</v>
+        <v>29.31011500075133</v>
       </c>
       <c r="D7">
-        <v>29.45581790103353</v>
+        <v>29.59031500075134</v>
       </c>
       <c r="E7">
-        <v>-6.5615</v>
+        <v>-6.2398</v>
       </c>
       <c r="F7">
-        <v>1.6085</v>
+        <v>1.9302</v>
       </c>
       <c r="G7">
         <v>1.65</v>
@@ -1861,28 +1861,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M7">
-        <v>0.08090755000000001</v>
+        <v>0.09708906000000002</v>
       </c>
       <c r="N7">
-        <v>8.113582245918369</v>
+        <v>8.097400735918368</v>
       </c>
       <c r="O7">
-        <v>2.19066720639796</v>
+        <v>2.18629819869796</v>
       </c>
       <c r="P7">
-        <v>5.92291503952041</v>
+        <v>5.911102537220408</v>
       </c>
       <c r="Q7">
-        <v>8.952915039520409</v>
+        <v>8.941102537220409</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09986109832476334</v>
+        <v>0.1002866798646699</v>
       </c>
       <c r="T7">
-        <v>0.990148001291576</v>
+        <v>0.9979426766530286</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>101.2821398734527</v>
+        <v>84.40178322787723</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09647261907278974</v>
+        <v>0.09624124473705428</v>
       </c>
       <c r="C8">
-        <v>29.31011500075133</v>
+        <v>29.1241459787078</v>
       </c>
       <c r="D8">
-        <v>29.59031500075134</v>
+        <v>29.7260459787078</v>
       </c>
       <c r="E8">
-        <v>-6.2398</v>
+        <v>-5.9181</v>
       </c>
       <c r="F8">
-        <v>1.9302</v>
+        <v>2.2519</v>
       </c>
       <c r="G8">
         <v>1.65</v>
@@ -1943,28 +1943,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M8">
-        <v>0.09708906</v>
+        <v>0.11327057</v>
       </c>
       <c r="N8">
-        <v>8.097400735918368</v>
+        <v>8.081219225918369</v>
       </c>
       <c r="O8">
-        <v>2.18629819869796</v>
+        <v>2.18192919099796</v>
       </c>
       <c r="P8">
-        <v>5.911102537220408</v>
+        <v>5.899290034920409</v>
       </c>
       <c r="Q8">
-        <v>8.941102537220409</v>
+        <v>8.92929003492041</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1002866798646699</v>
+        <v>0.1007214136957573</v>
       </c>
       <c r="T8">
-        <v>0.9979426766530286</v>
+        <v>1.005904979441609</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>84.40178322787725</v>
+        <v>72.34438562389479</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09624124473705427</v>
+        <v>0.09600987040131885</v>
       </c>
       <c r="C9">
-        <v>29.12414597870781</v>
+        <v>28.93942789257038</v>
       </c>
       <c r="D9">
-        <v>29.72604597870781</v>
+        <v>29.86302789257038</v>
       </c>
       <c r="E9">
-        <v>-5.918099999999999</v>
+        <v>-5.596399999999999</v>
       </c>
       <c r="F9">
-        <v>2.2519</v>
+        <v>2.5736</v>
       </c>
       <c r="G9">
         <v>1.65</v>
@@ -2025,28 +2025,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M9">
-        <v>0.11327057</v>
+        <v>0.12945208</v>
       </c>
       <c r="N9">
-        <v>8.081219225918369</v>
+        <v>8.065037715918368</v>
       </c>
       <c r="O9">
-        <v>2.18192919099796</v>
+        <v>2.17756018329796</v>
       </c>
       <c r="P9">
-        <v>5.899290034920409</v>
+        <v>5.887477532620409</v>
       </c>
       <c r="Q9">
-        <v>8.92929003492041</v>
+        <v>8.91747753262041</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1007214136957573</v>
+        <v>0.1011655982623031</v>
       </c>
       <c r="T9">
-        <v>1.005904979441609</v>
+        <v>1.014040375769072</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>72.34438562389479</v>
+        <v>63.30133742090794</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09600987040131885</v>
+        <v>0.0957784960655834</v>
       </c>
       <c r="C10">
-        <v>28.93942789257038</v>
+        <v>28.75597811587893</v>
       </c>
       <c r="D10">
-        <v>29.86302789257038</v>
+        <v>30.00127811587893</v>
       </c>
       <c r="E10">
-        <v>-5.596399999999999</v>
+        <v>-5.274699999999999</v>
       </c>
       <c r="F10">
-        <v>2.5736</v>
+        <v>2.8953</v>
       </c>
       <c r="G10">
         <v>1.65</v>
@@ -2107,28 +2107,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M10">
-        <v>0.12945208</v>
+        <v>0.14563359</v>
       </c>
       <c r="N10">
-        <v>8.065037715918368</v>
+        <v>8.048856205918369</v>
       </c>
       <c r="O10">
-        <v>2.17756018329796</v>
+        <v>2.17319117559796</v>
       </c>
       <c r="P10">
-        <v>5.887477532620409</v>
+        <v>5.875665030320409</v>
       </c>
       <c r="Q10">
-        <v>8.91747753262041</v>
+        <v>8.90566503032041</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1011655982623031</v>
+        <v>0.1016195451270147</v>
       </c>
       <c r="T10">
-        <v>1.014040375769072</v>
+        <v>1.022354572015819</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>63.30133742090794</v>
+        <v>56.26785548525151</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0957784960655834</v>
+        <v>0.09554712172984796</v>
       </c>
       <c r="C11">
-        <v>28.75597811587893</v>
+        <v>28.57381434539129</v>
       </c>
       <c r="D11">
-        <v>30.00127811587893</v>
+        <v>30.14081434539129</v>
       </c>
       <c r="E11">
-        <v>-5.274699999999999</v>
+        <v>-4.952999999999999</v>
       </c>
       <c r="F11">
-        <v>2.8953</v>
+        <v>3.217</v>
       </c>
       <c r="G11">
         <v>1.65</v>
@@ -2189,28 +2189,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M11">
-        <v>0.14563359</v>
+        <v>0.1618151</v>
       </c>
       <c r="N11">
-        <v>8.048856205918369</v>
+        <v>8.032674695918368</v>
       </c>
       <c r="O11">
-        <v>2.17319117559796</v>
+        <v>2.16882216789796</v>
       </c>
       <c r="P11">
-        <v>5.875665030320409</v>
+        <v>5.863852528020409</v>
       </c>
       <c r="Q11">
-        <v>8.90566503032041</v>
+        <v>8.89385252802041</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1016195451270147</v>
+        <v>0.1020835796998311</v>
       </c>
       <c r="T11">
-        <v>1.022354572015819</v>
+        <v>1.030853528179161</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>56.26785548525151</v>
+        <v>50.64106993672635</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09554712172984796</v>
+        <v>0.0953157473941125</v>
       </c>
       <c r="C12">
-        <v>28.57381434539129</v>
+        <v>28.3929546086349</v>
       </c>
       <c r="D12">
-        <v>30.14081434539129</v>
+        <v>30.2816546086349</v>
       </c>
       <c r="E12">
-        <v>-4.952999999999999</v>
+        <v>-4.6313</v>
       </c>
       <c r="F12">
-        <v>3.217000000000001</v>
+        <v>3.5387</v>
       </c>
       <c r="G12">
         <v>1.65</v>
@@ -2271,28 +2271,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M12">
-        <v>0.1618151</v>
+        <v>0.17799661</v>
       </c>
       <c r="N12">
-        <v>8.032674695918368</v>
+        <v>8.016493185918369</v>
       </c>
       <c r="O12">
-        <v>2.16882216789796</v>
+        <v>2.16445316019796</v>
       </c>
       <c r="P12">
-        <v>5.863852528020409</v>
+        <v>5.852040025720409</v>
       </c>
       <c r="Q12">
-        <v>8.89385252802041</v>
+        <v>8.882040025720411</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1020835796998311</v>
+        <v>0.1025580420158567</v>
       </c>
       <c r="T12">
-        <v>1.030853528179161</v>
+        <v>1.039543472121455</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.64106993672635</v>
+        <v>46.03733630611487</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0953157473941125</v>
+        <v>0.09508437305837707</v>
       </c>
       <c r="C13">
-        <v>28.3929546086349</v>
+        <v>28.21341727167099</v>
       </c>
       <c r="D13">
-        <v>30.2816546086349</v>
+        <v>30.42381727167099</v>
       </c>
       <c r="E13">
-        <v>-4.6313</v>
+        <v>-4.3096</v>
       </c>
       <c r="F13">
-        <v>3.5387</v>
+        <v>3.8604</v>
       </c>
       <c r="G13">
         <v>1.65</v>
@@ -2353,28 +2353,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M13">
-        <v>0.17799661</v>
+        <v>0.19417812</v>
       </c>
       <c r="N13">
-        <v>8.016493185918369</v>
+        <v>8.000311675918368</v>
       </c>
       <c r="O13">
-        <v>2.16445316019796</v>
+        <v>2.160084152497959</v>
       </c>
       <c r="P13">
-        <v>5.852040025720409</v>
+        <v>5.840227523420409</v>
       </c>
       <c r="Q13">
-        <v>8.882040025720411</v>
+        <v>8.870227523420409</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1025580420158567</v>
+        <v>0.1030432875663376</v>
       </c>
       <c r="T13">
-        <v>1.039543472121455</v>
+        <v>1.04843091478971</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>46.03733630611487</v>
+        <v>42.20089161393862</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09508437305837707</v>
+        <v>0.09485299872264161</v>
       </c>
       <c r="C14">
-        <v>28.21341727167099</v>
+        <v>28.03522104707872</v>
       </c>
       <c r="D14">
-        <v>30.42381727167099</v>
+        <v>30.56732104707872</v>
       </c>
       <c r="E14">
-        <v>-4.3096</v>
+        <v>-3.9879</v>
       </c>
       <c r="F14">
-        <v>3.8604</v>
+        <v>4.1821</v>
       </c>
       <c r="G14">
         <v>1.65</v>
@@ -2435,28 +2435,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M14">
-        <v>0.19417812</v>
+        <v>0.21035963</v>
       </c>
       <c r="N14">
-        <v>8.000311675918368</v>
+        <v>7.984130165918368</v>
       </c>
       <c r="O14">
-        <v>2.160084152497959</v>
+        <v>2.15571514479796</v>
       </c>
       <c r="P14">
-        <v>5.840227523420409</v>
+        <v>5.828415021120408</v>
       </c>
       <c r="Q14">
-        <v>8.870227523420409</v>
+        <v>8.858415021120408</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1030432875663376</v>
+        <v>0.1035396881869444</v>
       </c>
       <c r="T14">
-        <v>1.04843091478971</v>
+        <v>1.057522666484821</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>42.20089161393862</v>
+        <v>38.9546691820972</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09485299872264161</v>
+        <v>0.09462162438690616</v>
       </c>
       <c r="C15">
-        <v>28.03522104707872</v>
+        <v>27.85838500216615</v>
       </c>
       <c r="D15">
-        <v>30.56732104707872</v>
+        <v>30.71218500216615</v>
       </c>
       <c r="E15">
-        <v>-3.9879</v>
+        <v>-3.666199999999999</v>
       </c>
       <c r="F15">
-        <v>4.1821</v>
+        <v>4.503800000000001</v>
       </c>
       <c r="G15">
         <v>1.65</v>
@@ -2517,28 +2517,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M15">
-        <v>0.21035963</v>
+        <v>0.22654114</v>
       </c>
       <c r="N15">
-        <v>7.984130165918368</v>
+        <v>7.967948655918368</v>
       </c>
       <c r="O15">
-        <v>2.15571514479796</v>
+        <v>2.151346137097959</v>
       </c>
       <c r="P15">
-        <v>5.828415021120408</v>
+        <v>5.816602518820408</v>
       </c>
       <c r="Q15">
-        <v>8.858415021120408</v>
+        <v>8.846602518820408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1035396881869444</v>
+        <v>0.1040476330080304</v>
       </c>
       <c r="T15">
-        <v>1.057522666484821</v>
+        <v>1.066825854265864</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.9546691820972</v>
+        <v>36.17219281194739</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09462162438690616</v>
+        <v>0.0943902500511707</v>
       </c>
       <c r="C16">
-        <v>27.85838500216615</v>
+        <v>27.68292856741591</v>
       </c>
       <c r="D16">
-        <v>30.71218500216615</v>
+        <v>30.85842856741591</v>
       </c>
       <c r="E16">
-        <v>-3.666199999999999</v>
+        <v>-3.344499999999999</v>
       </c>
       <c r="F16">
-        <v>4.503800000000001</v>
+        <v>4.825500000000001</v>
       </c>
       <c r="G16">
         <v>1.65</v>
@@ -2599,28 +2599,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M16">
-        <v>0.22654114</v>
+        <v>0.24272265</v>
       </c>
       <c r="N16">
-        <v>7.967948655918368</v>
+        <v>7.951767145918368</v>
       </c>
       <c r="O16">
-        <v>2.151346137097959</v>
+        <v>2.14697712939796</v>
       </c>
       <c r="P16">
-        <v>5.816602518820408</v>
+        <v>5.804790016520409</v>
       </c>
       <c r="Q16">
-        <v>8.846602518820408</v>
+        <v>8.834790016520408</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040476330080304</v>
+        <v>0.1045675294719655</v>
       </c>
       <c r="T16">
-        <v>1.066825854265864</v>
+        <v>1.076347940582933</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>36.17219281194739</v>
+        <v>33.76071329115089</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0943902500511707</v>
+        <v>0.09415887571543527</v>
       </c>
       <c r="C17">
-        <v>27.68292856741591</v>
+        <v>27.50887154517327</v>
       </c>
       <c r="D17">
-        <v>30.85842856741591</v>
+        <v>31.00607154517328</v>
       </c>
       <c r="E17">
-        <v>-3.3445</v>
+        <v>-3.022799999999999</v>
       </c>
       <c r="F17">
-        <v>4.8255</v>
+        <v>5.147200000000001</v>
       </c>
       <c r="G17">
         <v>1.65</v>
@@ -2681,28 +2681,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M17">
-        <v>0.24272265</v>
+        <v>0.25890416</v>
       </c>
       <c r="N17">
-        <v>7.951767145918368</v>
+        <v>7.935585635918368</v>
       </c>
       <c r="O17">
-        <v>2.14697712939796</v>
+        <v>2.14260812169796</v>
       </c>
       <c r="P17">
-        <v>5.804790016520409</v>
+        <v>5.792977514220409</v>
       </c>
       <c r="Q17">
-        <v>8.834790016520408</v>
+        <v>8.822977514220408</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045675294719655</v>
+        <v>0.1050998044231372</v>
       </c>
       <c r="T17">
-        <v>1.076347940582933</v>
+        <v>1.086096743240884</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.76071329115091</v>
+        <v>31.65066871045397</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09415887571543527</v>
+        <v>0.09392750137969982</v>
       </c>
       <c r="C18">
-        <v>27.50887154517327</v>
+        <v>27.33623411858492</v>
       </c>
       <c r="D18">
-        <v>31.00607154517328</v>
+        <v>31.15513411858492</v>
       </c>
       <c r="E18">
-        <v>-3.022799999999999</v>
+        <v>-2.701099999999999</v>
       </c>
       <c r="F18">
-        <v>5.147200000000001</v>
+        <v>5.468900000000001</v>
       </c>
       <c r="G18">
         <v>1.65</v>
@@ -2763,28 +2763,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M18">
-        <v>0.25890416</v>
+        <v>0.27508567</v>
       </c>
       <c r="N18">
-        <v>7.935585635918368</v>
+        <v>7.919404125918368</v>
       </c>
       <c r="O18">
-        <v>2.14260812169796</v>
+        <v>2.13823911399796</v>
       </c>
       <c r="P18">
-        <v>5.792977514220409</v>
+        <v>5.781165011920409</v>
       </c>
       <c r="Q18">
-        <v>8.822977514220408</v>
+        <v>8.811165011920409</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1050998044231372</v>
+        <v>0.1056449052767468</v>
       </c>
       <c r="T18">
-        <v>1.086096743240884</v>
+        <v>1.096080456806256</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.65066871045397</v>
+        <v>29.78886466866256</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09392750137969982</v>
+        <v>0.09369612704396436</v>
       </c>
       <c r="C19">
-        <v>27.33623411858492</v>
+        <v>27.16503686079662</v>
       </c>
       <c r="D19">
-        <v>31.15513411858492</v>
+        <v>31.30563686079662</v>
       </c>
       <c r="E19">
-        <v>-2.701099999999999</v>
+        <v>-2.379399999999999</v>
       </c>
       <c r="F19">
-        <v>5.468900000000001</v>
+        <v>5.790600000000001</v>
       </c>
       <c r="G19">
         <v>1.65</v>
@@ -2845,28 +2845,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M19">
-        <v>0.27508567</v>
+        <v>0.2912671800000001</v>
       </c>
       <c r="N19">
-        <v>7.919404125918368</v>
+        <v>7.903222615918368</v>
       </c>
       <c r="O19">
-        <v>2.13823911399796</v>
+        <v>2.13387010629796</v>
       </c>
       <c r="P19">
-        <v>5.781165011920409</v>
+        <v>5.769352509620409</v>
       </c>
       <c r="Q19">
-        <v>8.811165011920409</v>
+        <v>8.799352509620409</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1056449052767468</v>
+        <v>0.1062033012731273</v>
       </c>
       <c r="T19">
-        <v>1.096080456806256</v>
+        <v>1.106307675580539</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.78886466866256</v>
+        <v>28.13392774262574</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09369612704396438</v>
+        <v>0.09346475270822893</v>
       </c>
       <c r="C20">
-        <v>27.1650368607966</v>
+        <v>26.99530074441897</v>
       </c>
       <c r="D20">
-        <v>31.3056368607966</v>
+        <v>31.45760074441897</v>
       </c>
       <c r="E20">
-        <v>-2.3794</v>
+        <v>-2.0577</v>
       </c>
       <c r="F20">
-        <v>5.7906</v>
+        <v>6.1123</v>
       </c>
       <c r="G20">
         <v>1.65</v>
@@ -2927,28 +2927,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M20">
-        <v>0.29126718</v>
+        <v>0.30744869</v>
       </c>
       <c r="N20">
-        <v>7.903222615918368</v>
+        <v>7.887041105918368</v>
       </c>
       <c r="O20">
-        <v>2.13387010629796</v>
+        <v>2.129501098597959</v>
       </c>
       <c r="P20">
-        <v>5.769352509620409</v>
+        <v>5.757540007320409</v>
       </c>
       <c r="Q20">
-        <v>8.799352509620409</v>
+        <v>8.787540007320409</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1062033012731273</v>
+        <v>0.106775484824974</v>
       </c>
       <c r="T20">
-        <v>1.106307675580539</v>
+        <v>1.116787418275174</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.13392774262575</v>
+        <v>26.65319470354018</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09346475270822893</v>
+        <v>0.0932333783724935</v>
       </c>
       <c r="C21">
-        <v>26.99530074441897</v>
+        <v>26.82704715127012</v>
       </c>
       <c r="D21">
-        <v>31.45760074441897</v>
+        <v>31.61104715127012</v>
       </c>
       <c r="E21">
-        <v>-2.0577</v>
+        <v>-1.735999999999999</v>
       </c>
       <c r="F21">
-        <v>6.1123</v>
+        <v>6.434000000000001</v>
       </c>
       <c r="G21">
         <v>1.65</v>
@@ -3009,28 +3009,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M21">
-        <v>0.30744869</v>
+        <v>0.3236302</v>
       </c>
       <c r="N21">
-        <v>7.887041105918368</v>
+        <v>7.870859595918368</v>
       </c>
       <c r="O21">
-        <v>2.129501098597959</v>
+        <v>2.12513209089796</v>
       </c>
       <c r="P21">
-        <v>5.757540007320409</v>
+        <v>5.745727505020408</v>
       </c>
       <c r="Q21">
-        <v>8.787540007320409</v>
+        <v>8.775727505020409</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.106775484824974</v>
+        <v>0.1073619729656169</v>
       </c>
       <c r="T21">
-        <v>1.116787418275174</v>
+        <v>1.127529154537176</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.65319470354018</v>
+        <v>25.32053496836317</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0932333783724935</v>
+        <v>0.09300200403675804</v>
       </c>
       <c r="C22">
-        <v>26.82704715127012</v>
+        <v>26.66029788240501</v>
       </c>
       <c r="D22">
-        <v>31.61104715127012</v>
+        <v>31.76599788240501</v>
       </c>
       <c r="E22">
-        <v>-1.735999999999999</v>
+        <v>-1.414299999999999</v>
       </c>
       <c r="F22">
-        <v>6.434000000000001</v>
+        <v>6.755700000000001</v>
       </c>
       <c r="G22">
         <v>1.65</v>
@@ -3091,28 +3091,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M22">
-        <v>0.3236302</v>
+        <v>0.33981171</v>
       </c>
       <c r="N22">
-        <v>7.870859595918368</v>
+        <v>7.854678085918368</v>
       </c>
       <c r="O22">
-        <v>2.12513209089796</v>
+        <v>2.120763083197959</v>
       </c>
       <c r="P22">
-        <v>5.745727505020408</v>
+        <v>5.733915002720408</v>
       </c>
       <c r="Q22">
-        <v>8.775727505020409</v>
+        <v>8.76391500272041</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1073619729656169</v>
+        <v>0.1079633089072887</v>
       </c>
       <c r="T22">
-        <v>1.127529154537176</v>
+        <v>1.138542833489355</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.32053496836317</v>
+        <v>24.11479520796493</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09300200403675804</v>
+        <v>0.09277062970102258</v>
       </c>
       <c r="C23">
-        <v>26.66029788240501</v>
+        <v>26.49507516844096</v>
       </c>
       <c r="D23">
-        <v>31.76599788240501</v>
+        <v>31.92247516844096</v>
       </c>
       <c r="E23">
-        <v>-1.4143</v>
+        <v>-1.092599999999999</v>
       </c>
       <c r="F23">
-        <v>6.7557</v>
+        <v>7.077400000000001</v>
       </c>
       <c r="G23">
         <v>1.65</v>
@@ -3173,28 +3173,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M23">
-        <v>0.33981171</v>
+        <v>0.35599322</v>
       </c>
       <c r="N23">
-        <v>7.854678085918368</v>
+        <v>7.838496575918368</v>
       </c>
       <c r="O23">
-        <v>2.120763083197959</v>
+        <v>2.11639407549796</v>
       </c>
       <c r="P23">
-        <v>5.733915002720408</v>
+        <v>5.722102500420409</v>
       </c>
       <c r="Q23">
-        <v>8.76391500272041</v>
+        <v>8.75210250042041</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1079633089072887</v>
+        <v>0.1085800637192597</v>
       </c>
       <c r="T23">
-        <v>1.138542833489355</v>
+        <v>1.149838914465949</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.11479520796493</v>
+        <v>23.01866815305743</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09277062970102258</v>
+        <v>0.09253925536528713</v>
       </c>
       <c r="C24">
-        <v>26.49507516844096</v>
+        <v>26.33140168019011</v>
       </c>
       <c r="D24">
-        <v>31.92247516844096</v>
+        <v>32.08050168019011</v>
       </c>
       <c r="E24">
-        <v>-1.092599999999999</v>
+        <v>-0.7708999999999993</v>
       </c>
       <c r="F24">
-        <v>7.077400000000001</v>
+        <v>7.399100000000001</v>
       </c>
       <c r="G24">
         <v>1.65</v>
@@ -3255,28 +3255,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M24">
-        <v>0.35599322</v>
+        <v>0.37217473</v>
       </c>
       <c r="N24">
-        <v>7.838496575918368</v>
+        <v>7.822315065918368</v>
       </c>
       <c r="O24">
-        <v>2.11639407549796</v>
+        <v>2.11202506779796</v>
       </c>
       <c r="P24">
-        <v>5.722102500420409</v>
+        <v>5.710289998120409</v>
       </c>
       <c r="Q24">
-        <v>8.75210250042041</v>
+        <v>8.74028999812041</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1085800637192597</v>
+        <v>0.1092128381367365</v>
       </c>
       <c r="T24">
-        <v>1.149838914465949</v>
+        <v>1.161428400143233</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>23.01866815305743</v>
+        <v>22.01785649422885</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09253925536528713</v>
+        <v>0.0923078810295517</v>
       </c>
       <c r="C25">
-        <v>26.33140168019011</v>
+        <v>26.16930053960916</v>
       </c>
       <c r="D25">
-        <v>32.08050168019011</v>
+        <v>32.24010053960916</v>
       </c>
       <c r="E25">
-        <v>-0.7708999999999993</v>
+        <v>-0.4491999999999985</v>
       </c>
       <c r="F25">
-        <v>7.399100000000001</v>
+        <v>7.720800000000001</v>
       </c>
       <c r="G25">
         <v>1.65</v>
@@ -3337,28 +3337,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M25">
-        <v>0.37217473</v>
+        <v>0.3883562400000001</v>
       </c>
       <c r="N25">
-        <v>7.822315065918368</v>
+        <v>7.806133555918368</v>
       </c>
       <c r="O25">
-        <v>2.11202506779796</v>
+        <v>2.107656060097959</v>
       </c>
       <c r="P25">
-        <v>5.710289998120409</v>
+        <v>5.698477495820409</v>
       </c>
       <c r="Q25">
-        <v>8.74028999812041</v>
+        <v>8.72847749582041</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1092128381367365</v>
+        <v>0.109862264512568</v>
       </c>
       <c r="T25">
-        <v>1.161428400143233</v>
+        <v>1.173322872285709</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>22.01785649422885</v>
+        <v>21.10044580696931</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0923078810295517</v>
+        <v>0.09207650669381624</v>
       </c>
       <c r="C26">
-        <v>26.16930053960916</v>
+        <v>26.00879533107758</v>
       </c>
       <c r="D26">
-        <v>32.24010053960916</v>
+        <v>32.40129533107758</v>
       </c>
       <c r="E26">
-        <v>-0.4491999999999994</v>
+        <v>-0.1274999999999995</v>
       </c>
       <c r="F26">
-        <v>7.720800000000001</v>
+        <v>8.0425</v>
       </c>
       <c r="G26">
         <v>1.65</v>
@@ -3419,28 +3419,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M26">
-        <v>0.38835624</v>
+        <v>0.40453775</v>
       </c>
       <c r="N26">
-        <v>7.806133555918368</v>
+        <v>7.789952045918368</v>
       </c>
       <c r="O26">
-        <v>2.107656060097959</v>
+        <v>2.10328705239796</v>
       </c>
       <c r="P26">
-        <v>5.698477495820409</v>
+        <v>5.686664993520409</v>
       </c>
       <c r="Q26">
-        <v>8.72847749582041</v>
+        <v>8.716664993520409</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.109862264512568</v>
+        <v>0.1105290089250883</v>
       </c>
       <c r="T26">
-        <v>1.173322872285709</v>
+        <v>1.185534530351985</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.10044580696931</v>
+        <v>20.25642797469054</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09207650669381624</v>
+        <v>0.09184513235808081</v>
       </c>
       <c r="C27">
-        <v>26.00879533107758</v>
+        <v>25.84991011301576</v>
       </c>
       <c r="D27">
-        <v>32.40129533107758</v>
+        <v>32.56411011301576</v>
       </c>
       <c r="E27">
-        <v>-0.1274999999999995</v>
+        <v>0.1942000000000004</v>
       </c>
       <c r="F27">
-        <v>8.0425</v>
+        <v>8.3642</v>
       </c>
       <c r="G27">
         <v>1.65</v>
@@ -3501,28 +3501,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M27">
-        <v>0.40453775</v>
+        <v>0.42071926</v>
       </c>
       <c r="N27">
-        <v>7.789952045918368</v>
+        <v>7.773770535918368</v>
       </c>
       <c r="O27">
-        <v>2.10328705239796</v>
+        <v>2.098918044697959</v>
       </c>
       <c r="P27">
-        <v>5.686664993520409</v>
+        <v>5.674852491220409</v>
       </c>
       <c r="Q27">
-        <v>8.716664993520409</v>
+        <v>8.704852491220409</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1105290089250883</v>
+        <v>0.1112137734568659</v>
       </c>
       <c r="T27">
-        <v>1.185534530351985</v>
+        <v>1.198076233230863</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.25642797469054</v>
+        <v>19.4773345910486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09184513235808081</v>
+        <v>0.09161375802234535</v>
       </c>
       <c r="C28">
-        <v>25.84991011301576</v>
+        <v>25.69266942985548</v>
       </c>
       <c r="D28">
-        <v>32.56411011301576</v>
+        <v>32.72856942985548</v>
       </c>
       <c r="E28">
-        <v>0.1942000000000004</v>
+        <v>0.5159000000000002</v>
       </c>
       <c r="F28">
-        <v>8.3642</v>
+        <v>8.6859</v>
       </c>
       <c r="G28">
         <v>1.65</v>
@@ -3583,28 +3583,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M28">
-        <v>0.42071926</v>
+        <v>0.43690077</v>
       </c>
       <c r="N28">
-        <v>7.773770535918368</v>
+        <v>7.757589025918368</v>
       </c>
       <c r="O28">
-        <v>2.098918044697959</v>
+        <v>2.09454903699796</v>
       </c>
       <c r="P28">
-        <v>5.674852491220409</v>
+        <v>5.663039988920408</v>
       </c>
       <c r="Q28">
-        <v>8.704852491220409</v>
+        <v>8.693039988920408</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1112137734568659</v>
+        <v>0.1119172986607471</v>
       </c>
       <c r="T28">
-        <v>1.198076233230863</v>
+        <v>1.210961544407792</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.4773345910486</v>
+        <v>18.75595182841717</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09161375802234535</v>
+        <v>0.09138238368660989</v>
       </c>
       <c r="C29">
-        <v>25.69266942985548</v>
+        <v>25.53709832437464</v>
       </c>
       <c r="D29">
-        <v>32.72856942985548</v>
+        <v>32.89469832437464</v>
       </c>
       <c r="E29">
-        <v>0.5159000000000002</v>
+        <v>0.8376000000000019</v>
       </c>
       <c r="F29">
-        <v>8.6859</v>
+        <v>9.007600000000002</v>
       </c>
       <c r="G29">
         <v>1.65</v>
@@ -3665,28 +3665,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M29">
-        <v>0.43690077</v>
+        <v>0.4530822800000001</v>
       </c>
       <c r="N29">
-        <v>7.757589025918368</v>
+        <v>7.741407515918368</v>
       </c>
       <c r="O29">
-        <v>2.09454903699796</v>
+        <v>2.09018002929796</v>
       </c>
       <c r="P29">
-        <v>5.663039988920408</v>
+        <v>5.651227486620408</v>
       </c>
       <c r="Q29">
-        <v>8.693039988920408</v>
+        <v>8.681227486620408</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1119172986607471</v>
+        <v>0.1126403662314026</v>
       </c>
       <c r="T29">
-        <v>1.210961544407792</v>
+        <v>1.224204780895191</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.75595182841717</v>
+        <v>18.0860964059737</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09138238368660989</v>
+        <v>0.09115100935087446</v>
       </c>
       <c r="C30">
-        <v>25.53709832437464</v>
+        <v>25.38322235040975</v>
       </c>
       <c r="D30">
-        <v>32.89469832437464</v>
+        <v>33.06252235040975</v>
       </c>
       <c r="E30">
-        <v>0.8376000000000019</v>
+        <v>1.159300000000002</v>
       </c>
       <c r="F30">
-        <v>9.007600000000002</v>
+        <v>9.329300000000002</v>
       </c>
       <c r="G30">
         <v>1.65</v>
@@ -3747,28 +3747,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M30">
-        <v>0.4530822800000001</v>
+        <v>0.4692637900000001</v>
       </c>
       <c r="N30">
-        <v>7.741407515918368</v>
+        <v>7.725226005918368</v>
       </c>
       <c r="O30">
-        <v>2.09018002929796</v>
+        <v>2.08581102159796</v>
       </c>
       <c r="P30">
-        <v>5.651227486620408</v>
+        <v>5.639414984320409</v>
       </c>
       <c r="Q30">
-        <v>8.681227486620408</v>
+        <v>8.669414984320408</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126403662314026</v>
+        <v>0.1133838019026401</v>
       </c>
       <c r="T30">
-        <v>1.224204780895191</v>
+        <v>1.237821066297728</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.0860964059737</v>
+        <v>17.46243790921598</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09115100935087446</v>
+        <v>0.09091963501513901</v>
       </c>
       <c r="C31">
-        <v>25.38322235040975</v>
+        <v>25.23106758595959</v>
       </c>
       <c r="D31">
-        <v>33.06252235040975</v>
+        <v>33.23206758595959</v>
       </c>
       <c r="E31">
-        <v>1.1593</v>
+        <v>1.481</v>
       </c>
       <c r="F31">
-        <v>9.3293</v>
+        <v>9.651</v>
       </c>
       <c r="G31">
         <v>1.65</v>
@@ -3829,28 +3829,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M31">
-        <v>0.46926379</v>
+        <v>0.4854453</v>
       </c>
       <c r="N31">
-        <v>7.725226005918368</v>
+        <v>7.709044495918368</v>
       </c>
       <c r="O31">
-        <v>2.08581102159796</v>
+        <v>2.08144201389796</v>
       </c>
       <c r="P31">
-        <v>5.639414984320409</v>
+        <v>5.627602482020409</v>
       </c>
       <c r="Q31">
-        <v>8.669414984320408</v>
+        <v>8.657602482020408</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1133838019026401</v>
+        <v>0.1141484785930557</v>
       </c>
       <c r="T31">
-        <v>1.237821066297728</v>
+        <v>1.251826388426052</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.46243790921599</v>
+        <v>16.88035664557545</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09091963501513901</v>
+        <v>0.09068826067940355</v>
       </c>
       <c r="C32">
-        <v>25.23106758595959</v>
+        <v>25.08066064669396</v>
       </c>
       <c r="D32">
-        <v>33.23206758595959</v>
+        <v>33.40336064669396</v>
       </c>
       <c r="E32">
-        <v>1.481</v>
+        <v>1.8027</v>
       </c>
       <c r="F32">
-        <v>9.651</v>
+        <v>9.9727</v>
       </c>
       <c r="G32">
         <v>1.65</v>
@@ -3911,28 +3911,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M32">
-        <v>0.4854453</v>
+        <v>0.50162681</v>
       </c>
       <c r="N32">
-        <v>7.709044495918368</v>
+        <v>7.692862985918368</v>
       </c>
       <c r="O32">
-        <v>2.08144201389796</v>
+        <v>2.077073006197959</v>
       </c>
       <c r="P32">
-        <v>5.627602482020409</v>
+        <v>5.615789979720409</v>
       </c>
       <c r="Q32">
-        <v>8.657602482020408</v>
+        <v>8.645789979720409</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1141484785930557</v>
+        <v>0.1149353198252226</v>
       </c>
       <c r="T32">
-        <v>1.251826388426052</v>
+        <v>1.266237661920415</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.88035664557545</v>
+        <v>16.33582901184721</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09068826067940355</v>
+        <v>0.09045688634366812</v>
       </c>
       <c r="C33">
-        <v>25.08066064669396</v>
+        <v>24.93202869988248</v>
       </c>
       <c r="D33">
-        <v>33.40336064669396</v>
+        <v>33.57642869988248</v>
       </c>
       <c r="E33">
-        <v>1.8027</v>
+        <v>2.124400000000001</v>
       </c>
       <c r="F33">
-        <v>9.9727</v>
+        <v>10.2944</v>
       </c>
       <c r="G33">
         <v>1.65</v>
@@ -3993,28 +3993,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M33">
-        <v>0.50162681</v>
+        <v>0.51780832</v>
       </c>
       <c r="N33">
-        <v>7.692862985918368</v>
+        <v>7.676681475918368</v>
       </c>
       <c r="O33">
-        <v>2.077073006197959</v>
+        <v>2.07270399849796</v>
       </c>
       <c r="P33">
-        <v>5.615789979720409</v>
+        <v>5.603977477420409</v>
       </c>
       <c r="Q33">
-        <v>8.645789979720409</v>
+        <v>8.633977477420409</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1149353198252226</v>
+        <v>0.1157453034465708</v>
       </c>
       <c r="T33">
-        <v>1.266237661920415</v>
+        <v>1.281072796399906</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.33582901184721</v>
+        <v>15.82533435522699</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09045688634366812</v>
+        <v>0.09022551200793266</v>
       </c>
       <c r="C34">
-        <v>24.93202869988248</v>
+        <v>24.78519947875876</v>
       </c>
       <c r="D34">
-        <v>33.57642869988248</v>
+        <v>33.75129947875876</v>
       </c>
       <c r="E34">
-        <v>2.124400000000001</v>
+        <v>2.446100000000001</v>
       </c>
       <c r="F34">
-        <v>10.2944</v>
+        <v>10.6161</v>
       </c>
       <c r="G34">
         <v>1.65</v>
@@ -4075,28 +4075,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M34">
-        <v>0.51780832</v>
+        <v>0.53398983</v>
       </c>
       <c r="N34">
-        <v>7.676681475918368</v>
+        <v>7.660499965918368</v>
       </c>
       <c r="O34">
-        <v>2.07270399849796</v>
+        <v>2.068334990797959</v>
       </c>
       <c r="P34">
-        <v>5.603977477420409</v>
+        <v>5.592164975120409</v>
       </c>
       <c r="Q34">
-        <v>8.633977477420409</v>
+        <v>8.622164975120409</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1157453034465708</v>
+        <v>0.1165794656834816</v>
       </c>
       <c r="T34">
-        <v>1.281072796399906</v>
+        <v>1.296350770714605</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.82533435522699</v>
+        <v>15.34577876870495</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09022551200793266</v>
+        <v>0.08999413767219722</v>
       </c>
       <c r="C35">
-        <v>24.78519947875876</v>
+        <v>24.64020129733544</v>
       </c>
       <c r="D35">
-        <v>33.75129947875876</v>
+        <v>33.92800129733545</v>
       </c>
       <c r="E35">
-        <v>2.446100000000001</v>
+        <v>2.767800000000001</v>
       </c>
       <c r="F35">
-        <v>10.6161</v>
+        <v>10.9378</v>
       </c>
       <c r="G35">
         <v>1.65</v>
@@ -4157,28 +4157,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M35">
-        <v>0.53398983</v>
+        <v>0.55017134</v>
       </c>
       <c r="N35">
-        <v>7.660499965918368</v>
+        <v>7.644318455918368</v>
       </c>
       <c r="O35">
-        <v>2.068334990797959</v>
+        <v>2.06396598309796</v>
       </c>
       <c r="P35">
-        <v>5.592164975120409</v>
+        <v>5.580352472820408</v>
       </c>
       <c r="Q35">
-        <v>8.622164975120409</v>
+        <v>8.610352472820409</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1165794656834816</v>
+        <v>0.1174389055639352</v>
       </c>
       <c r="T35">
-        <v>1.296350770714605</v>
+        <v>1.312091713947932</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.34577876870495</v>
+        <v>14.89443233433128</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08999413767219722</v>
+        <v>0.08976276333646177</v>
       </c>
       <c r="C36">
-        <v>24.64020129733544</v>
+        <v>24.49706306568752</v>
       </c>
       <c r="D36">
-        <v>33.92800129733545</v>
+        <v>34.10656306568752</v>
       </c>
       <c r="E36">
-        <v>2.767800000000001</v>
+        <v>3.089500000000001</v>
       </c>
       <c r="F36">
-        <v>10.9378</v>
+        <v>11.2595</v>
       </c>
       <c r="G36">
         <v>1.65</v>
@@ -4239,28 +4239,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M36">
-        <v>0.55017134</v>
+        <v>0.56635285</v>
       </c>
       <c r="N36">
-        <v>7.644318455918368</v>
+        <v>7.628136945918368</v>
       </c>
       <c r="O36">
-        <v>2.06396598309796</v>
+        <v>2.05959697539796</v>
       </c>
       <c r="P36">
-        <v>5.580352472820408</v>
+        <v>5.568539970520408</v>
       </c>
       <c r="Q36">
-        <v>8.610352472820409</v>
+        <v>8.59853997052041</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1174389055639352</v>
+        <v>0.1183247897484027</v>
       </c>
       <c r="T36">
-        <v>1.312091713947932</v>
+        <v>1.32831699389613</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.89443233433128</v>
+        <v>14.46887712477896</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08976276333646177</v>
+        <v>0.08953138900072632</v>
       </c>
       <c r="C37">
-        <v>24.49706306568752</v>
+        <v>24.35581430572042</v>
       </c>
       <c r="D37">
-        <v>34.10656306568752</v>
+        <v>34.28701430572043</v>
       </c>
       <c r="E37">
-        <v>3.089500000000001</v>
+        <v>3.411200000000003</v>
       </c>
       <c r="F37">
-        <v>11.2595</v>
+        <v>11.5812</v>
       </c>
       <c r="G37">
         <v>1.65</v>
@@ -4321,28 +4321,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M37">
-        <v>0.56635285</v>
+        <v>0.5825343600000001</v>
       </c>
       <c r="N37">
-        <v>7.628136945918368</v>
+        <v>7.611955435918368</v>
       </c>
       <c r="O37">
-        <v>2.05959697539796</v>
+        <v>2.055227967697959</v>
       </c>
       <c r="P37">
-        <v>5.568539970520408</v>
+        <v>5.556727468220409</v>
       </c>
       <c r="Q37">
-        <v>8.59853997052041</v>
+        <v>8.58672746822041</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1183247897484027</v>
+        <v>0.1192383578136349</v>
       </c>
       <c r="T37">
-        <v>1.32831699389613</v>
+        <v>1.34504931384271</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.46887712477896</v>
+        <v>14.06696387131287</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08953138900072634</v>
+        <v>0.08930001466499088</v>
       </c>
       <c r="C38">
-        <v>24.35581430572041</v>
+        <v>24.21648516744159</v>
       </c>
       <c r="D38">
-        <v>34.28701430572041</v>
+        <v>34.46938516744159</v>
       </c>
       <c r="E38">
-        <v>3.411200000000001</v>
+        <v>3.732900000000001</v>
       </c>
       <c r="F38">
-        <v>11.5812</v>
+        <v>11.9029</v>
       </c>
       <c r="G38">
         <v>1.65</v>
@@ -4403,28 +4403,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M38">
-        <v>0.58253436</v>
+        <v>0.59871587</v>
       </c>
       <c r="N38">
-        <v>7.611955435918368</v>
+        <v>7.595773925918368</v>
       </c>
       <c r="O38">
-        <v>2.055227967697959</v>
+        <v>2.05085895999796</v>
       </c>
       <c r="P38">
-        <v>5.556727468220409</v>
+        <v>5.544914965920409</v>
       </c>
       <c r="Q38">
-        <v>8.58672746822041</v>
+        <v>8.57491496592041</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1192383578136349</v>
+        <v>0.1201809280396681</v>
       </c>
       <c r="T38">
-        <v>1.34504931384271</v>
+        <v>1.362312818549498</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.06696387131287</v>
+        <v>13.68677565857469</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08930001466499088</v>
+        <v>0.08906864032925543</v>
       </c>
       <c r="C39">
-        <v>24.21648516744159</v>
+        <v>24.07910644575395</v>
       </c>
       <c r="D39">
-        <v>34.46938516744159</v>
+        <v>34.65370644575395</v>
       </c>
       <c r="E39">
-        <v>3.732900000000001</v>
+        <v>4.054600000000001</v>
       </c>
       <c r="F39">
-        <v>11.9029</v>
+        <v>12.2246</v>
       </c>
       <c r="G39">
         <v>1.65</v>
@@ -4485,28 +4485,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M39">
-        <v>0.59871587</v>
+        <v>0.61489738</v>
       </c>
       <c r="N39">
-        <v>7.595773925918368</v>
+        <v>7.579592415918368</v>
       </c>
       <c r="O39">
-        <v>2.05085895999796</v>
+        <v>2.046489952297959</v>
       </c>
       <c r="P39">
-        <v>5.544914965920409</v>
+        <v>5.533102463620409</v>
       </c>
       <c r="Q39">
-        <v>8.57491496592041</v>
+        <v>8.56310246362041</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1201809280396681</v>
+        <v>0.1211539037568636</v>
       </c>
       <c r="T39">
-        <v>1.362312818549498</v>
+        <v>1.380133210504892</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.68677565857469</v>
+        <v>13.32659735177009</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08906864032925543</v>
+        <v>0.08883726599351999</v>
       </c>
       <c r="C40">
-        <v>24.07910644575395</v>
+        <v>23.94370959779118</v>
       </c>
       <c r="D40">
-        <v>34.65370644575395</v>
+        <v>34.84000959779119</v>
       </c>
       <c r="E40">
-        <v>4.054600000000001</v>
+        <v>4.376300000000001</v>
       </c>
       <c r="F40">
-        <v>12.2246</v>
+        <v>12.5463</v>
       </c>
       <c r="G40">
         <v>1.65</v>
@@ -4567,28 +4567,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M40">
-        <v>0.61489738</v>
+        <v>0.6310788899999999</v>
       </c>
       <c r="N40">
-        <v>7.579592415918368</v>
+        <v>7.563410905918369</v>
       </c>
       <c r="O40">
-        <v>2.046489952297959</v>
+        <v>2.04212094459796</v>
       </c>
       <c r="P40">
-        <v>5.533102463620409</v>
+        <v>5.521289961320409</v>
       </c>
       <c r="Q40">
-        <v>8.56310246362041</v>
+        <v>8.551289961320411</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1211539037568636</v>
+        <v>0.1221587803172459</v>
       </c>
       <c r="T40">
-        <v>1.380133210504892</v>
+        <v>1.398537877606365</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.32659735177009</v>
+        <v>12.98488972736573</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08883726599351999</v>
+        <v>0.08904389165778455</v>
       </c>
       <c r="C41">
-        <v>23.94370959779118</v>
+        <v>23.45553891603349</v>
       </c>
       <c r="D41">
-        <v>34.84000959779119</v>
+        <v>34.67353891603349</v>
       </c>
       <c r="E41">
-        <v>4.376300000000001</v>
+        <v>4.698000000000002</v>
       </c>
       <c r="F41">
-        <v>12.5463</v>
+        <v>12.868</v>
       </c>
       <c r="G41">
         <v>1.65</v>
@@ -4649,45 +4649,45 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M41">
-        <v>0.6310788899999999</v>
+        <v>0.6665624000000001</v>
       </c>
       <c r="N41">
-        <v>7.563410905918369</v>
+        <v>7.527927395918368</v>
       </c>
       <c r="O41">
-        <v>2.04212094459796</v>
+        <v>2.032540396897959</v>
       </c>
       <c r="P41">
-        <v>5.521289961320409</v>
+        <v>5.495386999020409</v>
       </c>
       <c r="Q41">
-        <v>8.551289961320411</v>
+        <v>8.525386999020409</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1221587803172459</v>
+        <v>0.1231971527629742</v>
       </c>
       <c r="T41">
-        <v>1.398537877606365</v>
+        <v>1.417556033611221</v>
       </c>
       <c r="U41">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.98488972736573</v>
+        <v>12.29365742189834</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08904389165778455</v>
+        <v>0.0888234673220491</v>
       </c>
       <c r="C42">
-        <v>23.45553891603349</v>
+        <v>23.31148363550609</v>
       </c>
       <c r="D42">
-        <v>34.67353891603349</v>
+        <v>34.85118363550609</v>
       </c>
       <c r="E42">
-        <v>4.698000000000002</v>
+        <v>5.019700000000002</v>
       </c>
       <c r="F42">
-        <v>12.868</v>
+        <v>13.1897</v>
       </c>
       <c r="G42">
         <v>1.65</v>
@@ -4731,28 +4731,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M42">
-        <v>0.6665624000000001</v>
+        <v>0.6832264600000001</v>
       </c>
       <c r="N42">
-        <v>7.527927395918368</v>
+        <v>7.511263335918368</v>
       </c>
       <c r="O42">
-        <v>2.032540396897959</v>
+        <v>2.02804110069796</v>
       </c>
       <c r="P42">
-        <v>5.495386999020409</v>
+        <v>5.483222235220408</v>
       </c>
       <c r="Q42">
-        <v>8.525386999020409</v>
+        <v>8.513222235220407</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1231971527629742</v>
+        <v>0.1242707242746595</v>
       </c>
       <c r="T42">
-        <v>1.417556033611221</v>
+        <v>1.437218872870478</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.29365742189834</v>
+        <v>11.99381211892521</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0888234673220491</v>
+        <v>0.08860304298631366</v>
       </c>
       <c r="C43">
-        <v>23.31148363550609</v>
+        <v>23.16925800149699</v>
       </c>
       <c r="D43">
-        <v>34.85118363550609</v>
+        <v>35.030658001497</v>
       </c>
       <c r="E43">
-        <v>5.019700000000002</v>
+        <v>5.341400000000002</v>
       </c>
       <c r="F43">
-        <v>13.1897</v>
+        <v>13.5114</v>
       </c>
       <c r="G43">
         <v>1.65</v>
@@ -4813,28 +4813,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M43">
-        <v>0.6832264600000001</v>
+        <v>0.6998905200000001</v>
       </c>
       <c r="N43">
-        <v>7.511263335918368</v>
+        <v>7.494599275918368</v>
       </c>
       <c r="O43">
-        <v>2.02804110069796</v>
+        <v>2.02354180449796</v>
       </c>
       <c r="P43">
-        <v>5.483222235220408</v>
+        <v>5.471057471420409</v>
       </c>
       <c r="Q43">
-        <v>8.513222235220407</v>
+        <v>8.50105747142041</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1242707242746595</v>
+        <v>0.1253813154936443</v>
       </c>
       <c r="T43">
-        <v>1.437218872870478</v>
+        <v>1.45755974106971</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.99381211892521</v>
+        <v>11.7082451637127</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08860304298631366</v>
+        <v>0.08838261865057821</v>
       </c>
       <c r="C44">
-        <v>23.16925800149699</v>
+        <v>23.02889042691022</v>
       </c>
       <c r="D44">
-        <v>35.030658001497</v>
+        <v>35.21199042691022</v>
       </c>
       <c r="E44">
-        <v>5.3414</v>
+        <v>5.6631</v>
       </c>
       <c r="F44">
-        <v>13.5114</v>
+        <v>13.8331</v>
       </c>
       <c r="G44">
         <v>1.65</v>
@@ -4895,28 +4895,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M44">
-        <v>0.69989052</v>
+        <v>0.7165545799999999</v>
       </c>
       <c r="N44">
-        <v>7.494599275918368</v>
+        <v>7.477935215918368</v>
       </c>
       <c r="O44">
-        <v>2.02354180449796</v>
+        <v>2.01904250829796</v>
       </c>
       <c r="P44">
-        <v>5.471057471420409</v>
+        <v>5.458892707620409</v>
       </c>
       <c r="Q44">
-        <v>8.50105747142041</v>
+        <v>8.488892707620408</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1253813154936442</v>
+        <v>0.1265308748255758</v>
       </c>
       <c r="T44">
-        <v>1.457559741069709</v>
+        <v>1.478614323942598</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.7082451637127</v>
+        <v>11.43596039246357</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08838261865057821</v>
+        <v>0.08816219431484276</v>
       </c>
       <c r="C45">
-        <v>23.02889042691022</v>
+        <v>22.89040991601622</v>
       </c>
       <c r="D45">
-        <v>35.21199042691022</v>
+        <v>35.39520991601622</v>
       </c>
       <c r="E45">
-        <v>5.6631</v>
+        <v>5.984800000000002</v>
       </c>
       <c r="F45">
-        <v>13.8331</v>
+        <v>14.1548</v>
       </c>
       <c r="G45">
         <v>1.65</v>
@@ -4977,28 +4977,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M45">
-        <v>0.7165545799999999</v>
+        <v>0.73321864</v>
       </c>
       <c r="N45">
-        <v>7.477935215918368</v>
+        <v>7.461271155918368</v>
       </c>
       <c r="O45">
-        <v>2.01904250829796</v>
+        <v>2.014543212097959</v>
       </c>
       <c r="P45">
-        <v>5.458892707620409</v>
+        <v>5.446727943820409</v>
       </c>
       <c r="Q45">
-        <v>8.488892707620408</v>
+        <v>8.476727943820409</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265308748255758</v>
+        <v>0.1277214898479335</v>
       </c>
       <c r="T45">
-        <v>1.478614323942598</v>
+        <v>1.500420856203805</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.43596039246357</v>
+        <v>11.17605220172576</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08816219431484276</v>
+        <v>0.08794176997910733</v>
       </c>
       <c r="C46">
-        <v>22.89040991601622</v>
+        <v>22.75384607991779</v>
       </c>
       <c r="D46">
-        <v>35.39520991601622</v>
+        <v>35.58034607991779</v>
       </c>
       <c r="E46">
-        <v>5.984800000000002</v>
+        <v>6.306500000000002</v>
       </c>
       <c r="F46">
-        <v>14.1548</v>
+        <v>14.4765</v>
       </c>
       <c r="G46">
         <v>1.65</v>
@@ -5059,28 +5059,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M46">
-        <v>0.73321864</v>
+        <v>0.7498827</v>
       </c>
       <c r="N46">
-        <v>7.461271155918368</v>
+        <v>7.444607095918369</v>
       </c>
       <c r="O46">
-        <v>2.014543212097959</v>
+        <v>2.01004391589796</v>
       </c>
       <c r="P46">
-        <v>5.446727943820409</v>
+        <v>5.434563180020409</v>
       </c>
       <c r="Q46">
-        <v>8.476727943820409</v>
+        <v>8.464563180020409</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1277214898479335</v>
+        <v>0.1289553999620133</v>
       </c>
       <c r="T46">
-        <v>1.500420856203805</v>
+        <v>1.523020353274509</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.17605220172576</v>
+        <v>10.92769548613186</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08794176997910733</v>
+        <v>0.08772134564337186</v>
       </c>
       <c r="C47">
-        <v>22.75384607991779</v>
+        <v>22.61922915250383</v>
       </c>
       <c r="D47">
-        <v>35.58034607991779</v>
+        <v>35.76742915250384</v>
       </c>
       <c r="E47">
-        <v>6.306500000000002</v>
+        <v>6.628200000000001</v>
       </c>
       <c r="F47">
-        <v>14.4765</v>
+        <v>14.7982</v>
       </c>
       <c r="G47">
         <v>1.65</v>
@@ -5141,28 +5141,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M47">
-        <v>0.7498827</v>
+        <v>0.7665467600000001</v>
       </c>
       <c r="N47">
-        <v>7.444607095918369</v>
+        <v>7.427943035918369</v>
       </c>
       <c r="O47">
-        <v>2.01004391589796</v>
+        <v>2.00554461969796</v>
       </c>
       <c r="P47">
-        <v>5.434563180020409</v>
+        <v>5.422398416220409</v>
       </c>
       <c r="Q47">
-        <v>8.464563180020409</v>
+        <v>8.452398416220408</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1289553999620133</v>
+        <v>0.1302350104506886</v>
       </c>
       <c r="T47">
-        <v>1.523020353274509</v>
+        <v>1.54645686875524</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.92769548613186</v>
+        <v>10.69013688860725</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08772134564337186</v>
+        <v>0.08750092130763643</v>
       </c>
       <c r="C48">
-        <v>22.61922915250383</v>
+        <v>22.48659000690902</v>
       </c>
       <c r="D48">
-        <v>35.76742915250384</v>
+        <v>35.95649000690902</v>
       </c>
       <c r="E48">
-        <v>6.628200000000001</v>
+        <v>6.949900000000001</v>
       </c>
       <c r="F48">
-        <v>14.7982</v>
+        <v>15.1199</v>
       </c>
       <c r="G48">
         <v>1.65</v>
@@ -5223,28 +5223,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M48">
-        <v>0.7665467600000001</v>
+        <v>0.7832108200000001</v>
       </c>
       <c r="N48">
-        <v>7.427943035918369</v>
+        <v>7.411278975918369</v>
       </c>
       <c r="O48">
-        <v>2.00554461969796</v>
+        <v>2.001045323497959</v>
       </c>
       <c r="P48">
-        <v>5.422398416220409</v>
+        <v>5.410233652420409</v>
       </c>
       <c r="Q48">
-        <v>8.452398416220408</v>
+        <v>8.44023365242041</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1302350104506886</v>
+        <v>0.1315629081276159</v>
       </c>
       <c r="T48">
-        <v>1.54645686875524</v>
+        <v>1.570777781046565</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.69013688860725</v>
+        <v>10.46268716757305</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08750092130763643</v>
+        <v>0.08728049697190099</v>
       </c>
       <c r="C49">
-        <v>22.48659000690902</v>
+        <v>22.35596017249839</v>
       </c>
       <c r="D49">
-        <v>35.95649000690902</v>
+        <v>36.14756017249839</v>
       </c>
       <c r="E49">
-        <v>6.949900000000001</v>
+        <v>7.271600000000003</v>
       </c>
       <c r="F49">
-        <v>15.1199</v>
+        <v>15.4416</v>
       </c>
       <c r="G49">
         <v>1.65</v>
@@ -5305,28 +5305,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M49">
-        <v>0.7832108200000001</v>
+        <v>0.7998748800000002</v>
       </c>
       <c r="N49">
-        <v>7.411278975918369</v>
+        <v>7.394614915918369</v>
       </c>
       <c r="O49">
-        <v>2.001045323497959</v>
+        <v>1.99654602729796</v>
       </c>
       <c r="P49">
-        <v>5.410233652420409</v>
+        <v>5.398068888620409</v>
       </c>
       <c r="Q49">
-        <v>8.44023365242041</v>
+        <v>8.428068888620409</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1315629081276159</v>
+        <v>0.1329418787921173</v>
       </c>
       <c r="T49">
-        <v>1.570777781046565</v>
+        <v>1.596034113041402</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.46268716757305</v>
+        <v>10.24471451824861</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08728049697190098</v>
+        <v>0.08706007263616553</v>
       </c>
       <c r="C50">
-        <v>22.35596017249841</v>
+        <v>22.22737185239632</v>
       </c>
       <c r="D50">
-        <v>36.14756017249841</v>
+        <v>36.34067185239633</v>
       </c>
       <c r="E50">
-        <v>7.271600000000001</v>
+        <v>7.593300000000001</v>
       </c>
       <c r="F50">
-        <v>15.4416</v>
+        <v>15.7633</v>
       </c>
       <c r="G50">
         <v>1.65</v>
@@ -5387,28 +5387,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M50">
-        <v>0.7998748800000001</v>
+        <v>0.81653894</v>
       </c>
       <c r="N50">
-        <v>7.394614915918369</v>
+        <v>7.377950855918368</v>
       </c>
       <c r="O50">
-        <v>1.99654602729796</v>
+        <v>1.99204673109796</v>
       </c>
       <c r="P50">
-        <v>5.398068888620409</v>
+        <v>5.385904124820408</v>
       </c>
       <c r="Q50">
-        <v>8.428068888620409</v>
+        <v>8.415904124820408</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1329418787921173</v>
+        <v>0.1343749267375794</v>
       </c>
       <c r="T50">
-        <v>1.596034113041402</v>
+        <v>1.622280889428193</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.24471451824861</v>
+        <v>10.03563871175374</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08706007263616553</v>
+        <v>0.08683964830043009</v>
       </c>
       <c r="C51">
-        <v>22.22737185239632</v>
+        <v>22.10085794158023</v>
       </c>
       <c r="D51">
-        <v>36.34067185239633</v>
+        <v>36.53585794158023</v>
       </c>
       <c r="E51">
-        <v>7.593300000000001</v>
+        <v>7.915000000000001</v>
       </c>
       <c r="F51">
-        <v>15.7633</v>
+        <v>16.085</v>
       </c>
       <c r="G51">
         <v>1.65</v>
@@ -5469,28 +5469,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M51">
-        <v>0.81653894</v>
+        <v>0.833203</v>
       </c>
       <c r="N51">
-        <v>7.377950855918368</v>
+        <v>7.361286795918368</v>
       </c>
       <c r="O51">
-        <v>1.99204673109796</v>
+        <v>1.98754743489796</v>
       </c>
       <c r="P51">
-        <v>5.385904124820408</v>
+        <v>5.373739361020409</v>
       </c>
       <c r="Q51">
-        <v>8.415904124820408</v>
+        <v>8.40373936102041</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1343749267375794</v>
+        <v>0.1358652966008602</v>
       </c>
       <c r="T51">
-        <v>1.622280889428193</v>
+        <v>1.649577536870456</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.03563871175374</v>
+        <v>9.834925937518669</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08683964830043009</v>
+        <v>0.08725213396469464</v>
       </c>
       <c r="C52">
-        <v>22.10085794158023</v>
+        <v>21.41559360384689</v>
       </c>
       <c r="D52">
-        <v>36.53585794158023</v>
+        <v>36.17229360384689</v>
       </c>
       <c r="E52">
-        <v>7.915000000000001</v>
+        <v>8.236700000000001</v>
       </c>
       <c r="F52">
-        <v>16.085</v>
+        <v>16.4067</v>
       </c>
       <c r="G52">
         <v>1.65</v>
@@ -5551,45 +5551,45 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M52">
-        <v>0.833203</v>
+        <v>0.87775845</v>
       </c>
       <c r="N52">
-        <v>7.361286795918368</v>
+        <v>7.316731345918368</v>
       </c>
       <c r="O52">
-        <v>1.98754743489796</v>
+        <v>1.97551746339796</v>
       </c>
       <c r="P52">
-        <v>5.373739361020409</v>
+        <v>5.341213882520409</v>
       </c>
       <c r="Q52">
-        <v>8.40373936102041</v>
+        <v>8.371213882520408</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1358652966008602</v>
+        <v>0.1374164978871319</v>
       </c>
       <c r="T52">
-        <v>1.649577536870456</v>
+        <v>1.677988333187914</v>
       </c>
       <c r="U52">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>9.834925937518669</v>
+        <v>9.335700266876803</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08725213396469464</v>
+        <v>0.08704411962895918</v>
       </c>
       <c r="C53">
-        <v>21.41559360384689</v>
+        <v>21.27632823195201</v>
       </c>
       <c r="D53">
-        <v>36.17229360384689</v>
+        <v>36.35472823195201</v>
       </c>
       <c r="E53">
-        <v>8.236700000000001</v>
+        <v>8.558400000000001</v>
       </c>
       <c r="F53">
-        <v>16.4067</v>
+        <v>16.7284</v>
       </c>
       <c r="G53">
         <v>1.65</v>
@@ -5633,28 +5633,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M53">
-        <v>0.87775845</v>
+        <v>0.8949694</v>
       </c>
       <c r="N53">
-        <v>7.316731345918368</v>
+        <v>7.299520395918369</v>
       </c>
       <c r="O53">
-        <v>1.97551746339796</v>
+        <v>1.97087050689796</v>
       </c>
       <c r="P53">
-        <v>5.341213882520409</v>
+        <v>5.328649889020409</v>
       </c>
       <c r="Q53">
-        <v>8.371213882520408</v>
+        <v>8.358649889020409</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1374164978871319</v>
+        <v>0.1390323325603317</v>
       </c>
       <c r="T53">
-        <v>1.677988333187914</v>
+        <v>1.707582912685265</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.335700266876803</v>
+        <v>9.156167569436864</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08704411962895918</v>
+        <v>0.08683610529322375</v>
       </c>
       <c r="C54">
-        <v>21.27632823195201</v>
+        <v>21.13891240292719</v>
       </c>
       <c r="D54">
-        <v>36.35472823195201</v>
+        <v>36.53901240292719</v>
       </c>
       <c r="E54">
-        <v>8.558400000000001</v>
+        <v>8.880100000000001</v>
       </c>
       <c r="F54">
-        <v>16.7284</v>
+        <v>17.0501</v>
       </c>
       <c r="G54">
         <v>1.65</v>
@@ -5715,28 +5715,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M54">
-        <v>0.8949694</v>
+        <v>0.91218035</v>
       </c>
       <c r="N54">
-        <v>7.299520395918369</v>
+        <v>7.282309445918369</v>
       </c>
       <c r="O54">
-        <v>1.97087050689796</v>
+        <v>1.96622355039796</v>
       </c>
       <c r="P54">
-        <v>5.328649889020409</v>
+        <v>5.316085895520409</v>
       </c>
       <c r="Q54">
-        <v>8.358649889020409</v>
+        <v>8.34608589552041</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1390323325603317</v>
+        <v>0.1407169261557952</v>
       </c>
       <c r="T54">
-        <v>1.707582912685265</v>
+        <v>1.738436835991015</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.156167569436864</v>
+        <v>8.983409690768244</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08683610529322375</v>
+        <v>0.08662809095748829</v>
       </c>
       <c r="C55">
-        <v>21.13891240292719</v>
+        <v>21.00337438638457</v>
       </c>
       <c r="D55">
-        <v>36.53901240292719</v>
+        <v>36.72517438638457</v>
       </c>
       <c r="E55">
-        <v>8.880100000000001</v>
+        <v>9.2018</v>
       </c>
       <c r="F55">
-        <v>17.0501</v>
+        <v>17.3718</v>
       </c>
       <c r="G55">
         <v>1.65</v>
@@ -5797,28 +5797,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M55">
-        <v>0.91218035</v>
+        <v>0.9293913</v>
       </c>
       <c r="N55">
-        <v>7.282309445918369</v>
+        <v>7.265098495918369</v>
       </c>
       <c r="O55">
-        <v>1.96622355039796</v>
+        <v>1.96157659389796</v>
       </c>
       <c r="P55">
-        <v>5.316085895520409</v>
+        <v>5.303521902020409</v>
       </c>
       <c r="Q55">
-        <v>8.34608589552041</v>
+        <v>8.333521902020408</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1407169261557952</v>
+        <v>0.1424747629510615</v>
       </c>
       <c r="T55">
-        <v>1.738436835991015</v>
+        <v>1.770632234223101</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.983409690768244</v>
+        <v>8.817050252050313</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08662809095748829</v>
+        <v>0.08642007662175286</v>
       </c>
       <c r="C56">
-        <v>21.00337438638457</v>
+        <v>20.86974303100797</v>
       </c>
       <c r="D56">
-        <v>36.72517438638457</v>
+        <v>36.91324303100797</v>
       </c>
       <c r="E56">
-        <v>9.2018</v>
+        <v>9.523500000000004</v>
       </c>
       <c r="F56">
-        <v>17.3718</v>
+        <v>17.6935</v>
       </c>
       <c r="G56">
         <v>1.65</v>
@@ -5879,28 +5879,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M56">
-        <v>0.9293913</v>
+        <v>0.9466022500000002</v>
       </c>
       <c r="N56">
-        <v>7.265098495918369</v>
+        <v>7.247887545918369</v>
       </c>
       <c r="O56">
-        <v>1.96157659389796</v>
+        <v>1.95692963739796</v>
       </c>
       <c r="P56">
-        <v>5.303521902020409</v>
+        <v>5.290957908520409</v>
       </c>
       <c r="Q56">
-        <v>8.333521902020408</v>
+        <v>8.320957908520409</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1424747629510615</v>
+        <v>0.1443107258261175</v>
       </c>
       <c r="T56">
-        <v>1.770632234223101</v>
+        <v>1.80425853904328</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.817050252050313</v>
+        <v>8.656740247467578</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08642007662175286</v>
+        <v>0.08621206228601741</v>
       </c>
       <c r="C57">
-        <v>20.86974303100797</v>
+        <v>20.73804777945638</v>
       </c>
       <c r="D57">
-        <v>36.91324303100797</v>
+        <v>37.10324777945638</v>
       </c>
       <c r="E57">
-        <v>9.523500000000004</v>
+        <v>9.845200000000004</v>
       </c>
       <c r="F57">
-        <v>17.6935</v>
+        <v>18.0152</v>
       </c>
       <c r="G57">
         <v>1.65</v>
@@ -5961,28 +5961,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M57">
-        <v>0.9466022500000002</v>
+        <v>0.9638132000000001</v>
       </c>
       <c r="N57">
-        <v>7.247887545918369</v>
+        <v>7.230676595918368</v>
       </c>
       <c r="O57">
-        <v>1.95692963739796</v>
+        <v>1.952282680897959</v>
       </c>
       <c r="P57">
-        <v>5.290957908520409</v>
+        <v>5.278393915020408</v>
       </c>
       <c r="Q57">
-        <v>8.320957908520409</v>
+        <v>8.308393915020408</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1443107258261175</v>
+        <v>0.1462301415591305</v>
       </c>
       <c r="T57">
-        <v>1.80425853904328</v>
+        <v>1.839413312264377</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.656740247467578</v>
+        <v>8.502155600191372</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08621206228601741</v>
+        <v>0.08600404795028196</v>
       </c>
       <c r="C58">
-        <v>20.73804777945638</v>
+        <v>20.60831868372989</v>
       </c>
       <c r="D58">
-        <v>37.10324777945638</v>
+        <v>37.2952186837299</v>
       </c>
       <c r="E58">
-        <v>9.845200000000004</v>
+        <v>10.1669</v>
       </c>
       <c r="F58">
-        <v>18.0152</v>
+        <v>18.3369</v>
       </c>
       <c r="G58">
         <v>1.65</v>
@@ -6043,28 +6043,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M58">
-        <v>0.9638132000000001</v>
+        <v>0.9810241500000002</v>
       </c>
       <c r="N58">
-        <v>7.230676595918368</v>
+        <v>7.213465645918368</v>
       </c>
       <c r="O58">
-        <v>1.952282680897959</v>
+        <v>1.947635724397959</v>
       </c>
       <c r="P58">
-        <v>5.278393915020408</v>
+        <v>5.265829921520409</v>
       </c>
       <c r="Q58">
-        <v>8.308393915020408</v>
+        <v>8.295829921520408</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1462301415591305</v>
+        <v>0.1482388324425162</v>
       </c>
       <c r="T58">
-        <v>1.839413312264377</v>
+        <v>1.876203191216687</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.502155600191372</v>
+        <v>8.352994975626611</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08600404795028196</v>
+        <v>0.08579603361454652</v>
       </c>
       <c r="C59">
-        <v>20.60831868372989</v>
+        <v>20.48058642101529</v>
       </c>
       <c r="D59">
-        <v>37.2952186837299</v>
+        <v>37.48918642101529</v>
       </c>
       <c r="E59">
-        <v>10.1669</v>
+        <v>10.4886</v>
       </c>
       <c r="F59">
-        <v>18.3369</v>
+        <v>18.6586</v>
       </c>
       <c r="G59">
         <v>1.65</v>
@@ -6125,28 +6125,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M59">
-        <v>0.9810241500000002</v>
+        <v>0.9982351000000002</v>
       </c>
       <c r="N59">
-        <v>7.213465645918368</v>
+        <v>7.196254695918368</v>
       </c>
       <c r="O59">
-        <v>1.947635724397959</v>
+        <v>1.942988767897959</v>
       </c>
       <c r="P59">
-        <v>5.265829921520409</v>
+        <v>5.253265928020409</v>
       </c>
       <c r="Q59">
-        <v>8.295829921520408</v>
+        <v>8.283265928020409</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1482388324425162</v>
+        <v>0.1503431752727298</v>
       </c>
       <c r="T59">
-        <v>1.876203191216687</v>
+        <v>1.914744969166726</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.352994975626611</v>
+        <v>8.208977820874427</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08579603361454652</v>
+        <v>0.08558801927881107</v>
       </c>
       <c r="C60">
-        <v>20.48058642101529</v>
+        <v>20.35488231002861</v>
       </c>
       <c r="D60">
-        <v>37.48918642101529</v>
+        <v>37.68518231002862</v>
       </c>
       <c r="E60">
-        <v>10.4886</v>
+        <v>10.8103</v>
       </c>
       <c r="F60">
-        <v>18.6586</v>
+        <v>18.9803</v>
       </c>
       <c r="G60">
         <v>1.65</v>
@@ -6207,28 +6207,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M60">
-        <v>0.9982350999999999</v>
+        <v>1.01544605</v>
       </c>
       <c r="N60">
-        <v>7.196254695918369</v>
+        <v>7.179043745918369</v>
       </c>
       <c r="O60">
-        <v>1.94298876789796</v>
+        <v>1.93834181139796</v>
       </c>
       <c r="P60">
-        <v>5.253265928020409</v>
+        <v>5.240701934520409</v>
       </c>
       <c r="Q60">
-        <v>8.283265928020409</v>
+        <v>8.27070193452041</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1503431752727298</v>
+        <v>0.1525501689727099</v>
       </c>
       <c r="T60">
-        <v>1.914744969166725</v>
+        <v>1.955166833846035</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.208977820874431</v>
+        <v>8.069842603571473</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08558801927881107</v>
+        <v>0.08538000494307561</v>
       </c>
       <c r="C61">
-        <v>20.35488231002861</v>
+        <v>20.23123832787309</v>
       </c>
       <c r="D61">
-        <v>37.68518231002862</v>
+        <v>37.88323832787309</v>
       </c>
       <c r="E61">
-        <v>10.8103</v>
+        <v>11.132</v>
       </c>
       <c r="F61">
-        <v>18.9803</v>
+        <v>19.302</v>
       </c>
       <c r="G61">
         <v>1.65</v>
@@ -6289,28 +6289,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M61">
-        <v>1.01544605</v>
+        <v>1.032657</v>
       </c>
       <c r="N61">
-        <v>7.179043745918369</v>
+        <v>7.161832795918368</v>
       </c>
       <c r="O61">
-        <v>1.93834181139796</v>
+        <v>1.93369485489796</v>
       </c>
       <c r="P61">
-        <v>5.240701934520409</v>
+        <v>5.228137941020409</v>
       </c>
       <c r="Q61">
-        <v>8.27070193452041</v>
+        <v>8.258137941020408</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1525501689727099</v>
+        <v>0.154867512357689</v>
       </c>
       <c r="T61">
-        <v>1.955166833846035</v>
+        <v>1.99760979175931</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.069842603571473</v>
+        <v>7.935345226845282</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08538000494307561</v>
+        <v>0.08517199060734018</v>
       </c>
       <c r="C62">
-        <v>20.23123832787309</v>
+        <v>20.10968712743139</v>
       </c>
       <c r="D62">
-        <v>37.88323832787309</v>
+        <v>38.08338712743139</v>
       </c>
       <c r="E62">
-        <v>11.132</v>
+        <v>11.4537</v>
       </c>
       <c r="F62">
-        <v>19.302</v>
+        <v>19.6237</v>
       </c>
       <c r="G62">
         <v>1.65</v>
@@ -6371,28 +6371,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M62">
-        <v>1.032657</v>
+        <v>1.04986795</v>
       </c>
       <c r="N62">
-        <v>7.161832795918368</v>
+        <v>7.144621845918369</v>
       </c>
       <c r="O62">
-        <v>1.93369485489796</v>
+        <v>1.92904789839796</v>
       </c>
       <c r="P62">
-        <v>5.228137941020409</v>
+        <v>5.21557394752041</v>
       </c>
       <c r="Q62">
-        <v>8.258137941020408</v>
+        <v>8.245573947520409</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.154867512357689</v>
+        <v>0.1573036938649748</v>
       </c>
       <c r="T62">
-        <v>1.99760979175931</v>
+        <v>2.042229311616855</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.935345226845282</v>
+        <v>7.805257600175689</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08517199060734018</v>
+        <v>0.08496397627160472</v>
       </c>
       <c r="C63">
-        <v>20.10968712743139</v>
+        <v>19.99026205531231</v>
       </c>
       <c r="D63">
-        <v>38.08338712743139</v>
+        <v>38.28566205531231</v>
       </c>
       <c r="E63">
-        <v>11.4537</v>
+        <v>11.7754</v>
       </c>
       <c r="F63">
-        <v>19.6237</v>
+        <v>19.9454</v>
       </c>
       <c r="G63">
         <v>1.65</v>
@@ -6453,28 +6453,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M63">
-        <v>1.04986795</v>
+        <v>1.0670789</v>
       </c>
       <c r="N63">
-        <v>7.144621845918369</v>
+        <v>7.127410895918368</v>
       </c>
       <c r="O63">
-        <v>1.92904789839796</v>
+        <v>1.92440094189796</v>
       </c>
       <c r="P63">
-        <v>5.21557394752041</v>
+        <v>5.203009954020409</v>
       </c>
       <c r="Q63">
-        <v>8.245573947520409</v>
+        <v>8.23300995402041</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1573036938649748</v>
+        <v>0.1598680954515914</v>
       </c>
       <c r="T63">
-        <v>2.042229311616855</v>
+        <v>2.089197227256376</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.805257600175689</v>
+        <v>7.67936634855995</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08496397627160472</v>
+        <v>0.08512388193586928</v>
       </c>
       <c r="C64">
-        <v>19.99026205531231</v>
+        <v>19.51287818278041</v>
       </c>
       <c r="D64">
-        <v>38.28566205531231</v>
+        <v>38.12997818278041</v>
       </c>
       <c r="E64">
-        <v>11.7754</v>
+        <v>12.0971</v>
       </c>
       <c r="F64">
-        <v>19.9454</v>
+        <v>20.2671</v>
       </c>
       <c r="G64">
         <v>1.65</v>
@@ -6535,45 +6535,45 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M64">
-        <v>1.0670789</v>
+        <v>1.10050353</v>
       </c>
       <c r="N64">
-        <v>7.127410895918368</v>
+        <v>7.093986265918368</v>
       </c>
       <c r="O64">
-        <v>1.92440094189796</v>
+        <v>1.91537629179796</v>
       </c>
       <c r="P64">
-        <v>5.203009954020409</v>
+        <v>5.178609974120409</v>
       </c>
       <c r="Q64">
-        <v>8.23300995402041</v>
+        <v>8.20860997412041</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1598680954515914</v>
+        <v>0.1625711133401872</v>
       </c>
       <c r="T64">
-        <v>2.089197227256376</v>
+        <v>2.138703949146683</v>
       </c>
       <c r="U64">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.67936634855995</v>
+        <v>7.446127679316365</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08512388193586928</v>
+        <v>0.08492170760013383</v>
       </c>
       <c r="C65">
-        <v>19.51287818278041</v>
+        <v>19.38822742944173</v>
       </c>
       <c r="D65">
-        <v>38.12997818278041</v>
+        <v>38.32702742944173</v>
       </c>
       <c r="E65">
-        <v>12.0971</v>
+        <v>12.4188</v>
       </c>
       <c r="F65">
-        <v>20.2671</v>
+        <v>20.5888</v>
       </c>
       <c r="G65">
         <v>1.65</v>
@@ -6617,28 +6617,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M65">
-        <v>1.10050353</v>
+        <v>1.11797184</v>
       </c>
       <c r="N65">
-        <v>7.093986265918368</v>
+        <v>7.076517955918368</v>
       </c>
       <c r="O65">
-        <v>1.91537629179796</v>
+        <v>1.91065984809796</v>
       </c>
       <c r="P65">
-        <v>5.178609974120409</v>
+        <v>5.165858107820409</v>
       </c>
       <c r="Q65">
-        <v>8.20860997412041</v>
+        <v>8.19585810782041</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1625711133401872</v>
+        <v>0.1654242988892607</v>
       </c>
       <c r="T65">
-        <v>2.138703949146683</v>
+        <v>2.19096104447534</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.446127679316365</v>
+        <v>7.329781934327046</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08492170760013383</v>
+        <v>0.08471953326439839</v>
       </c>
       <c r="C66">
-        <v>19.38822742944173</v>
+        <v>19.26562388978776</v>
       </c>
       <c r="D66">
-        <v>38.32702742944173</v>
+        <v>38.52612388978776</v>
       </c>
       <c r="E66">
-        <v>12.4188</v>
+        <v>12.7405</v>
       </c>
       <c r="F66">
-        <v>20.5888</v>
+        <v>20.9105</v>
       </c>
       <c r="G66">
         <v>1.65</v>
@@ -6699,28 +6699,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M66">
-        <v>1.11797184</v>
+        <v>1.13544015</v>
       </c>
       <c r="N66">
-        <v>7.076517955918368</v>
+        <v>7.059049645918368</v>
       </c>
       <c r="O66">
-        <v>1.91065984809796</v>
+        <v>1.90594340439796</v>
       </c>
       <c r="P66">
-        <v>5.165858107820409</v>
+        <v>5.153106241520409</v>
       </c>
       <c r="Q66">
-        <v>8.19585810782041</v>
+        <v>8.183106241520409</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1654242988892607</v>
+        <v>0.1684405236125668</v>
       </c>
       <c r="T66">
-        <v>2.19096104447534</v>
+        <v>2.246204259537063</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.329781934327046</v>
+        <v>7.217016058414322</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08471953326439839</v>
+        <v>0.08451735892866294</v>
       </c>
       <c r="C67">
-        <v>19.26562388978776</v>
+        <v>19.14509963424468</v>
       </c>
       <c r="D67">
-        <v>38.52612388978776</v>
+        <v>38.72729963424469</v>
       </c>
       <c r="E67">
-        <v>12.7405</v>
+        <v>13.0622</v>
       </c>
       <c r="F67">
-        <v>20.9105</v>
+        <v>21.2322</v>
       </c>
       <c r="G67">
         <v>1.65</v>
@@ -6781,28 +6781,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M67">
-        <v>1.13544015</v>
+        <v>1.15290846</v>
       </c>
       <c r="N67">
-        <v>7.059049645918368</v>
+        <v>7.041581335918369</v>
       </c>
       <c r="O67">
-        <v>1.90594340439796</v>
+        <v>1.90122696069796</v>
       </c>
       <c r="P67">
-        <v>5.153106241520409</v>
+        <v>5.140354375220409</v>
       </c>
       <c r="Q67">
-        <v>8.183106241520409</v>
+        <v>8.170354375220409</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1684405236125668</v>
+        <v>0.1716341733195969</v>
       </c>
       <c r="T67">
-        <v>2.246204259537063</v>
+        <v>2.304697075484769</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.217016058414322</v>
+        <v>7.10766733025653</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08451735892866294</v>
+        <v>0.0843151845929275</v>
       </c>
       <c r="C68">
-        <v>19.14509963424468</v>
+        <v>19.02668740661637</v>
       </c>
       <c r="D68">
-        <v>38.72729963424469</v>
+        <v>38.93058740661638</v>
       </c>
       <c r="E68">
-        <v>13.0622</v>
+        <v>13.3839</v>
       </c>
       <c r="F68">
-        <v>21.2322</v>
+        <v>21.5539</v>
       </c>
       <c r="G68">
         <v>1.65</v>
@@ -6863,28 +6863,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M68">
-        <v>1.15290846</v>
+        <v>1.17037677</v>
       </c>
       <c r="N68">
-        <v>7.041581335918369</v>
+        <v>7.024113025918369</v>
       </c>
       <c r="O68">
-        <v>1.90122696069796</v>
+        <v>1.89651051699796</v>
       </c>
       <c r="P68">
-        <v>5.140354375220409</v>
+        <v>5.127602508920409</v>
       </c>
       <c r="Q68">
-        <v>8.170354375220409</v>
+        <v>8.157602508920409</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1716341733195969</v>
+        <v>0.1750213775543258</v>
       </c>
       <c r="T68">
-        <v>2.304697075484769</v>
+        <v>2.366734910580822</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.10766733025653</v>
+        <v>7.001582743237776</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0843151845929275</v>
+        <v>0.08411301025719206</v>
       </c>
       <c r="C69">
-        <v>19.02668740661637</v>
+        <v>18.91042064185128</v>
       </c>
       <c r="D69">
-        <v>38.93058740661638</v>
+        <v>39.13602064185128</v>
       </c>
       <c r="E69">
-        <v>13.3839</v>
+        <v>13.7056</v>
       </c>
       <c r="F69">
-        <v>21.5539</v>
+        <v>21.8756</v>
       </c>
       <c r="G69">
         <v>1.65</v>
@@ -6945,28 +6945,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M69">
-        <v>1.17037677</v>
+        <v>1.18784508</v>
       </c>
       <c r="N69">
-        <v>7.024113025918369</v>
+        <v>7.006644715918368</v>
       </c>
       <c r="O69">
-        <v>1.89651051699796</v>
+        <v>1.891794073297959</v>
       </c>
       <c r="P69">
-        <v>5.127602508920409</v>
+        <v>5.114850642620408</v>
       </c>
       <c r="Q69">
-        <v>8.157602508920409</v>
+        <v>8.144850642620408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1750213775543258</v>
+        <v>0.1786202820537252</v>
       </c>
       <c r="T69">
-        <v>2.366734910580822</v>
+        <v>2.432650110370377</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.001582743237776</v>
+        <v>6.898618291131337</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08411301025719206</v>
+        <v>0.08391083592145659</v>
       </c>
       <c r="C70">
-        <v>18.91042064185128</v>
+        <v>18.79633348437466</v>
       </c>
       <c r="D70">
-        <v>39.13602064185128</v>
+        <v>39.34363348437466</v>
       </c>
       <c r="E70">
-        <v>13.7056</v>
+        <v>14.0273</v>
       </c>
       <c r="F70">
-        <v>21.8756</v>
+        <v>22.1973</v>
       </c>
       <c r="G70">
         <v>1.65</v>
@@ -7027,28 +7027,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M70">
-        <v>1.18784508</v>
+        <v>1.20531339</v>
       </c>
       <c r="N70">
-        <v>7.006644715918368</v>
+        <v>6.989176405918368</v>
       </c>
       <c r="O70">
-        <v>1.891794073297959</v>
+        <v>1.887077629597959</v>
       </c>
       <c r="P70">
-        <v>5.114850642620408</v>
+        <v>5.102098776320409</v>
       </c>
       <c r="Q70">
-        <v>8.144850642620408</v>
+        <v>8.132098776320408</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1786202820537252</v>
+        <v>0.1824513739401826</v>
       </c>
       <c r="T70">
-        <v>2.432650110370377</v>
+        <v>2.502817903694742</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.898618291131337</v>
+        <v>6.79863831589755</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08391083592145659</v>
+        <v>0.08370866158572116</v>
       </c>
       <c r="C71">
-        <v>18.79633348437466</v>
+        <v>18.68446080700739</v>
       </c>
       <c r="D71">
-        <v>39.34363348437466</v>
+        <v>39.5534608070074</v>
       </c>
       <c r="E71">
-        <v>14.0273</v>
+        <v>14.349</v>
       </c>
       <c r="F71">
-        <v>22.1973</v>
+        <v>22.519</v>
       </c>
       <c r="G71">
         <v>1.65</v>
@@ -7109,28 +7109,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M71">
-        <v>1.20531339</v>
+        <v>1.2227817</v>
       </c>
       <c r="N71">
-        <v>6.989176405918368</v>
+        <v>6.971708095918368</v>
       </c>
       <c r="O71">
-        <v>1.887077629597959</v>
+        <v>1.882361185897959</v>
       </c>
       <c r="P71">
-        <v>5.102098776320409</v>
+        <v>5.089346910020408</v>
       </c>
       <c r="Q71">
-        <v>8.132098776320408</v>
+        <v>8.119346910020408</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1824513739401826</v>
+        <v>0.1865378719524039</v>
       </c>
       <c r="T71">
-        <v>2.502817903694742</v>
+        <v>2.5776635499074</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.79863831589755</v>
+        <v>6.701514911384728</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08370866158572116</v>
+        <v>0.08350648724998572</v>
       </c>
       <c r="C72">
-        <v>18.68446080700739</v>
+        <v>18.57483823049364</v>
       </c>
       <c r="D72">
-        <v>39.5534608070074</v>
+        <v>39.76553823049365</v>
       </c>
       <c r="E72">
-        <v>14.349</v>
+        <v>14.67070000000001</v>
       </c>
       <c r="F72">
-        <v>22.519</v>
+        <v>22.84070000000001</v>
       </c>
       <c r="G72">
         <v>1.65</v>
@@ -7191,28 +7191,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M72">
-        <v>1.2227817</v>
+        <v>1.24025001</v>
       </c>
       <c r="N72">
-        <v>6.971708095918368</v>
+        <v>6.954239785918368</v>
       </c>
       <c r="O72">
-        <v>1.882361185897959</v>
+        <v>1.877644742197959</v>
       </c>
       <c r="P72">
-        <v>5.089346910020408</v>
+        <v>5.076595043720409</v>
       </c>
       <c r="Q72">
-        <v>8.119346910020408</v>
+        <v>8.106595043720409</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1865378719524039</v>
+        <v>0.1909061974137439</v>
       </c>
       <c r="T72">
-        <v>2.5776635499074</v>
+        <v>2.657670964824378</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.701514911384728</v>
+        <v>6.607127377421563</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08350648724998572</v>
+        <v>0.08330431291425026</v>
       </c>
       <c r="C73">
-        <v>18.57483823049364</v>
+        <v>18.46750214365997</v>
       </c>
       <c r="D73">
-        <v>39.76553823049365</v>
+        <v>39.97990214365998</v>
       </c>
       <c r="E73">
-        <v>14.6707</v>
+        <v>14.9924</v>
       </c>
       <c r="F73">
-        <v>22.8407</v>
+        <v>23.1624</v>
       </c>
       <c r="G73">
         <v>1.65</v>
@@ -7273,28 +7273,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M73">
-        <v>1.24025001</v>
+        <v>1.25771832</v>
       </c>
       <c r="N73">
-        <v>6.954239785918368</v>
+        <v>6.936771475918368</v>
       </c>
       <c r="O73">
-        <v>1.877644742197959</v>
+        <v>1.87292829849796</v>
       </c>
       <c r="P73">
-        <v>5.076595043720409</v>
+        <v>5.063843177420408</v>
       </c>
       <c r="Q73">
-        <v>8.106595043720409</v>
+        <v>8.093843177420409</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1909061974137438</v>
+        <v>0.1955865461223224</v>
       </c>
       <c r="T73">
-        <v>2.657670964824377</v>
+        <v>2.743393195092568</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.607127377421564</v>
+        <v>6.515361719401819</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08330431291425026</v>
+        <v>0.08310213857851481</v>
       </c>
       <c r="C74">
-        <v>18.46750214365997</v>
+        <v>18.36248972422991</v>
       </c>
       <c r="D74">
-        <v>39.97990214365998</v>
+        <v>40.19658972422991</v>
       </c>
       <c r="E74">
-        <v>14.9924</v>
+        <v>15.3141</v>
       </c>
       <c r="F74">
-        <v>23.1624</v>
+        <v>23.4841</v>
       </c>
       <c r="G74">
         <v>1.65</v>
@@ -7355,28 +7355,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M74">
-        <v>1.25771832</v>
+        <v>1.27518663</v>
       </c>
       <c r="N74">
-        <v>6.936771475918368</v>
+        <v>6.919303165918368</v>
       </c>
       <c r="O74">
-        <v>1.87292829849796</v>
+        <v>1.86821185479796</v>
       </c>
       <c r="P74">
-        <v>5.063843177420408</v>
+        <v>5.051091311120409</v>
       </c>
       <c r="Q74">
-        <v>8.093843177420409</v>
+        <v>8.08109131112041</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1955865461223224</v>
+        <v>0.2006135873278326</v>
       </c>
       <c r="T74">
-        <v>2.743393195092568</v>
+        <v>2.835465220195438</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.515361719401819</v>
+        <v>6.426110188999055</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08310213857851481</v>
+        <v>0.08289996424277937</v>
       </c>
       <c r="C75">
-        <v>18.36248972422991</v>
+        <v>18.25983896031934</v>
       </c>
       <c r="D75">
-        <v>40.19658972422991</v>
+        <v>40.41563896031934</v>
       </c>
       <c r="E75">
-        <v>15.3141</v>
+        <v>15.6358</v>
       </c>
       <c r="F75">
-        <v>23.4841</v>
+        <v>23.8058</v>
       </c>
       <c r="G75">
         <v>1.65</v>
@@ -7437,28 +7437,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M75">
-        <v>1.27518663</v>
+        <v>1.29265494</v>
       </c>
       <c r="N75">
-        <v>6.919303165918368</v>
+        <v>6.901834855918368</v>
       </c>
       <c r="O75">
-        <v>1.86821185479796</v>
+        <v>1.86349541109796</v>
       </c>
       <c r="P75">
-        <v>5.051091311120409</v>
+        <v>5.038339444820409</v>
       </c>
       <c r="Q75">
-        <v>8.08109131112041</v>
+        <v>8.06833944482041</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2006135873278326</v>
+        <v>0.2060273240106899</v>
       </c>
       <c r="T75">
-        <v>2.835465220195438</v>
+        <v>2.934619708767761</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.426110188999055</v>
+        <v>6.339270862120689</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08289996424277937</v>
+        <v>0.08269778990704392</v>
       </c>
       <c r="C76">
-        <v>18.25983896031934</v>
+        <v>18.15958867263847</v>
       </c>
       <c r="D76">
-        <v>40.41563896031934</v>
+        <v>40.63708867263847</v>
       </c>
       <c r="E76">
-        <v>15.6358</v>
+        <v>15.9575</v>
       </c>
       <c r="F76">
-        <v>23.8058</v>
+        <v>24.1275</v>
       </c>
       <c r="G76">
         <v>1.65</v>
@@ -7519,28 +7519,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M76">
-        <v>1.29265494</v>
+        <v>1.31012325</v>
       </c>
       <c r="N76">
-        <v>6.901834855918368</v>
+        <v>6.884366545918368</v>
       </c>
       <c r="O76">
-        <v>1.86349541109796</v>
+        <v>1.85877896739796</v>
       </c>
       <c r="P76">
-        <v>5.038339444820409</v>
+        <v>5.025587578520408</v>
       </c>
       <c r="Q76">
-        <v>8.06833944482041</v>
+        <v>8.055587578520409</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2060273240106899</v>
+        <v>0.2118741596281757</v>
       </c>
       <c r="T76">
-        <v>2.934619708767761</v>
+        <v>3.04170655642587</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.339270862120689</v>
+        <v>6.254747250625746</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08269778990704392</v>
+        <v>0.08249561557130849</v>
       </c>
       <c r="C77">
-        <v>18.15958867263847</v>
+        <v>18.06177853742755</v>
       </c>
       <c r="D77">
-        <v>40.63708867263847</v>
+        <v>40.86097853742755</v>
       </c>
       <c r="E77">
-        <v>15.9575</v>
+        <v>16.2792</v>
       </c>
       <c r="F77">
-        <v>24.1275</v>
+        <v>24.4492</v>
       </c>
       <c r="G77">
         <v>1.65</v>
@@ -7601,28 +7601,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M77">
-        <v>1.31012325</v>
+        <v>1.32759156</v>
       </c>
       <c r="N77">
-        <v>6.884366545918368</v>
+        <v>6.866898235918368</v>
       </c>
       <c r="O77">
-        <v>1.85877896739796</v>
+        <v>1.85406252369796</v>
       </c>
       <c r="P77">
-        <v>5.025587578520408</v>
+        <v>5.012835712220409</v>
       </c>
       <c r="Q77">
-        <v>8.055587578520409</v>
+        <v>8.042835712220409</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2118741596281757</v>
+        <v>0.2182082315471187</v>
       </c>
       <c r="T77">
-        <v>3.04170655642587</v>
+        <v>3.157717308055489</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.254747250625746</v>
+        <v>6.172447944696461</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08249561557130849</v>
+        <v>0.08285554123557302</v>
       </c>
       <c r="C78">
-        <v>18.06177853742755</v>
+        <v>17.34319012743007</v>
       </c>
       <c r="D78">
-        <v>40.86097853742755</v>
+        <v>40.46409012743008</v>
       </c>
       <c r="E78">
-        <v>16.2792</v>
+        <v>16.6009</v>
       </c>
       <c r="F78">
-        <v>24.4492</v>
+        <v>24.7709</v>
       </c>
       <c r="G78">
         <v>1.65</v>
@@ -7683,45 +7683,45 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M78">
-        <v>1.32759156</v>
+        <v>1.36983077</v>
       </c>
       <c r="N78">
-        <v>6.866898235918368</v>
+        <v>6.824659025918368</v>
       </c>
       <c r="O78">
-        <v>1.85406252369796</v>
+        <v>1.84265793699796</v>
       </c>
       <c r="P78">
-        <v>5.012835712220409</v>
+        <v>4.982001088920409</v>
       </c>
       <c r="Q78">
-        <v>8.042835712220409</v>
+        <v>8.01200108892041</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2182082315471187</v>
+        <v>0.2250930923285784</v>
       </c>
       <c r="T78">
-        <v>3.157717308055489</v>
+        <v>3.28381595113116</v>
       </c>
       <c r="U78">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>6.172447944696461</v>
+        <v>5.982118357524096</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08285554123557302</v>
+        <v>0.08266066689983759</v>
       </c>
       <c r="C79">
-        <v>17.34319012743007</v>
+        <v>17.23541497871259</v>
       </c>
       <c r="D79">
-        <v>40.46409012743008</v>
+        <v>40.67801497871259</v>
       </c>
       <c r="E79">
-        <v>16.6009</v>
+        <v>16.9226</v>
       </c>
       <c r="F79">
-        <v>24.7709</v>
+        <v>25.0926</v>
       </c>
       <c r="G79">
         <v>1.65</v>
@@ -7765,28 +7765,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M79">
-        <v>1.36983077</v>
+        <v>1.38762078</v>
       </c>
       <c r="N79">
-        <v>6.824659025918368</v>
+        <v>6.806869015918369</v>
       </c>
       <c r="O79">
-        <v>1.84265793699796</v>
+        <v>1.83785463429796</v>
       </c>
       <c r="P79">
-        <v>4.982001088920409</v>
+        <v>4.96901438162041</v>
       </c>
       <c r="Q79">
-        <v>8.01200108892041</v>
+        <v>7.99901438162041</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2250930923285784</v>
+        <v>0.2326038495447163</v>
       </c>
       <c r="T79">
-        <v>3.28381595113116</v>
+        <v>3.421378107213711</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.982118357524096</v>
+        <v>5.905424532427634</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08266066689983759</v>
+        <v>0.08246579256410214</v>
       </c>
       <c r="C80">
-        <v>17.23541497871259</v>
+        <v>17.12991380038416</v>
       </c>
       <c r="D80">
-        <v>40.67801497871259</v>
+        <v>40.89421380038416</v>
       </c>
       <c r="E80">
-        <v>16.9226</v>
+        <v>17.2443</v>
       </c>
       <c r="F80">
-        <v>25.0926</v>
+        <v>25.4143</v>
       </c>
       <c r="G80">
         <v>1.65</v>
@@ -7847,28 +7847,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M80">
-        <v>1.38762078</v>
+        <v>1.40541079</v>
       </c>
       <c r="N80">
-        <v>6.806869015918369</v>
+        <v>6.789079005918368</v>
       </c>
       <c r="O80">
-        <v>1.83785463429796</v>
+        <v>1.83305133159796</v>
       </c>
       <c r="P80">
-        <v>4.96901438162041</v>
+        <v>4.956027674320408</v>
       </c>
       <c r="Q80">
-        <v>7.99901438162041</v>
+        <v>7.986027674320408</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2326038495447163</v>
+        <v>0.240829916971915</v>
       </c>
       <c r="T80">
-        <v>3.421378107213711</v>
+        <v>3.572041421018409</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.905424532427634</v>
+        <v>5.830672323156397</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08246579256410214</v>
+        <v>0.08227091822836669</v>
       </c>
       <c r="C81">
-        <v>17.12991380038416</v>
+        <v>17.02672304382774</v>
       </c>
       <c r="D81">
-        <v>40.89421380038416</v>
+        <v>41.11272304382775</v>
       </c>
       <c r="E81">
-        <v>17.2443</v>
+        <v>17.566</v>
       </c>
       <c r="F81">
-        <v>25.4143</v>
+        <v>25.736</v>
       </c>
       <c r="G81">
         <v>1.65</v>
@@ -7929,28 +7929,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M81">
-        <v>1.40541079</v>
+        <v>1.4232008</v>
       </c>
       <c r="N81">
-        <v>6.789079005918368</v>
+        <v>6.771288995918368</v>
       </c>
       <c r="O81">
-        <v>1.83305133159796</v>
+        <v>1.82824802889796</v>
       </c>
       <c r="P81">
-        <v>4.956027674320408</v>
+        <v>4.943040967020409</v>
       </c>
       <c r="Q81">
-        <v>7.986027674320408</v>
+        <v>7.973040967020409</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.240829916971915</v>
+        <v>0.2498785911418335</v>
       </c>
       <c r="T81">
-        <v>3.572041421018409</v>
+        <v>3.737771066203578</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.830672323156397</v>
+        <v>5.757788919116942</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08227091822836669</v>
+        <v>0.08207604389263123</v>
       </c>
       <c r="C82">
-        <v>17.02672304382774</v>
+        <v>16.92587994369132</v>
       </c>
       <c r="D82">
-        <v>41.11272304382775</v>
+        <v>41.33357994369133</v>
       </c>
       <c r="E82">
-        <v>17.566</v>
+        <v>17.8877</v>
       </c>
       <c r="F82">
-        <v>25.736</v>
+        <v>26.0577</v>
       </c>
       <c r="G82">
         <v>1.65</v>
@@ -8011,28 +8011,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M82">
-        <v>1.4232008</v>
+        <v>1.44099081</v>
       </c>
       <c r="N82">
-        <v>6.771288995918368</v>
+        <v>6.753498985918368</v>
       </c>
       <c r="O82">
-        <v>1.82824802889796</v>
+        <v>1.823444726197959</v>
       </c>
       <c r="P82">
-        <v>4.943040967020409</v>
+        <v>4.930054259720409</v>
       </c>
       <c r="Q82">
-        <v>7.973040967020409</v>
+        <v>7.960054259720409</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2498785911418335</v>
+        <v>0.2598797573296381</v>
       </c>
       <c r="T82">
-        <v>3.737771066203578</v>
+        <v>3.920945937197711</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.757788919116942</v>
+        <v>5.686705105300684</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08207604389263123</v>
+        <v>0.08188116955689578</v>
       </c>
       <c r="C83">
-        <v>16.92587994369132</v>
+        <v>16.82742253903994</v>
       </c>
       <c r="D83">
-        <v>41.33357994369133</v>
+        <v>41.55682253903994</v>
       </c>
       <c r="E83">
-        <v>17.8877</v>
+        <v>18.2094</v>
       </c>
       <c r="F83">
-        <v>26.0577</v>
+        <v>26.3794</v>
       </c>
       <c r="G83">
         <v>1.65</v>
@@ -8093,28 +8093,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M83">
-        <v>1.44099081</v>
+        <v>1.45878082</v>
       </c>
       <c r="N83">
-        <v>6.753498985918368</v>
+        <v>6.735708975918368</v>
       </c>
       <c r="O83">
-        <v>1.823444726197959</v>
+        <v>1.81864142349796</v>
       </c>
       <c r="P83">
-        <v>4.930054259720409</v>
+        <v>4.917067552420408</v>
       </c>
       <c r="Q83">
-        <v>7.960054259720409</v>
+        <v>7.947067552420409</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2598797573296381</v>
+        <v>0.2709921642049767</v>
       </c>
       <c r="T83">
-        <v>3.920945937197711</v>
+        <v>4.124473571635638</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.686705105300684</v>
+        <v>5.617355043040919</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08188116955689578</v>
+        <v>0.08168629522116036</v>
       </c>
       <c r="C84">
-        <v>16.82742253903994</v>
+        <v>16.73138969519695</v>
       </c>
       <c r="D84">
-        <v>41.55682253903994</v>
+        <v>41.78248969519695</v>
       </c>
       <c r="E84">
-        <v>18.2094</v>
+        <v>18.5311</v>
       </c>
       <c r="F84">
-        <v>26.3794</v>
+        <v>26.7011</v>
       </c>
       <c r="G84">
         <v>1.65</v>
@@ -8175,28 +8175,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M84">
-        <v>1.45878082</v>
+        <v>1.47657083</v>
       </c>
       <c r="N84">
-        <v>6.735708975918368</v>
+        <v>6.717918965918368</v>
       </c>
       <c r="O84">
-        <v>1.81864142349796</v>
+        <v>1.81383812079796</v>
       </c>
       <c r="P84">
-        <v>4.917067552420408</v>
+        <v>4.904080845120409</v>
       </c>
       <c r="Q84">
-        <v>7.947067552420409</v>
+        <v>7.934080845120409</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2709921642049767</v>
+        <v>0.2834119130656492</v>
       </c>
       <c r="T84">
-        <v>4.124473571635638</v>
+        <v>4.351945633654497</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.617355043040919</v>
+        <v>5.54967606661874</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08168629522116036</v>
+        <v>0.08149142088542491</v>
       </c>
       <c r="C85">
-        <v>16.73138969519695</v>
+        <v>16.63782112630089</v>
       </c>
       <c r="D85">
-        <v>41.78248969519695</v>
+        <v>42.01062112630089</v>
       </c>
       <c r="E85">
-        <v>18.5311</v>
+        <v>18.8528</v>
       </c>
       <c r="F85">
-        <v>26.7011</v>
+        <v>27.0228</v>
       </c>
       <c r="G85">
         <v>1.65</v>
@@ -8257,28 +8257,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M85">
-        <v>1.47657083</v>
+        <v>1.49436084</v>
       </c>
       <c r="N85">
-        <v>6.717918965918368</v>
+        <v>6.700128955918368</v>
       </c>
       <c r="O85">
-        <v>1.81383812079796</v>
+        <v>1.809034818097959</v>
       </c>
       <c r="P85">
-        <v>4.904080845120409</v>
+        <v>4.891094137820408</v>
       </c>
       <c r="Q85">
-        <v>7.934080845120409</v>
+        <v>7.921094137820408</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2834119130656492</v>
+        <v>0.2973841305339058</v>
       </c>
       <c r="T85">
-        <v>4.351945633654497</v>
+        <v>4.607851703425714</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.54967606661874</v>
+        <v>5.483608494397087</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08149142088542491</v>
+        <v>0.08129654654968946</v>
       </c>
       <c r="C86">
-        <v>16.63782112630089</v>
+        <v>16.54675741860502</v>
       </c>
       <c r="D86">
-        <v>42.01062112630089</v>
+        <v>42.24125741860502</v>
       </c>
       <c r="E86">
-        <v>18.8528</v>
+        <v>19.1745</v>
       </c>
       <c r="F86">
-        <v>27.0228</v>
+        <v>27.3445</v>
       </c>
       <c r="G86">
         <v>1.65</v>
@@ -8339,28 +8339,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M86">
-        <v>1.49436084</v>
+        <v>1.51215085</v>
       </c>
       <c r="N86">
-        <v>6.700128955918368</v>
+        <v>6.682338945918368</v>
       </c>
       <c r="O86">
-        <v>1.809034818097959</v>
+        <v>1.80423151539796</v>
       </c>
       <c r="P86">
-        <v>4.891094137820408</v>
+        <v>4.878107430520409</v>
       </c>
       <c r="Q86">
-        <v>7.921094137820408</v>
+        <v>7.908107430520409</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2973841305339056</v>
+        <v>0.313219310331263</v>
       </c>
       <c r="T86">
-        <v>4.607851703425711</v>
+        <v>4.897878582499755</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.483608494397088</v>
+        <v>5.419095453286534</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08129654654968946</v>
+        <v>0.08110167221395401</v>
       </c>
       <c r="C87">
-        <v>16.54675741860502</v>
+        <v>16.45824005454903</v>
       </c>
       <c r="D87">
-        <v>42.24125741860502</v>
+        <v>42.47444005454903</v>
       </c>
       <c r="E87">
-        <v>19.1745</v>
+        <v>19.4962</v>
       </c>
       <c r="F87">
-        <v>27.3445</v>
+        <v>27.6662</v>
       </c>
       <c r="G87">
         <v>1.65</v>
@@ -8421,28 +8421,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M87">
-        <v>1.51215085</v>
+        <v>1.52994086</v>
       </c>
       <c r="N87">
-        <v>6.682338945918368</v>
+        <v>6.664548935918368</v>
       </c>
       <c r="O87">
-        <v>1.80423151539796</v>
+        <v>1.79942821269796</v>
       </c>
       <c r="P87">
-        <v>4.878107430520409</v>
+        <v>4.865120723220409</v>
       </c>
       <c r="Q87">
-        <v>7.908107430520409</v>
+        <v>7.895120723220409</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.313219310331263</v>
+        <v>0.3313166586711001</v>
       </c>
       <c r="T87">
-        <v>4.897878582499755</v>
+        <v>5.229337872870092</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.419095453286534</v>
+        <v>5.356082715457622</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08110167221395401</v>
+        <v>0.08090679787821857</v>
       </c>
       <c r="C88">
-        <v>16.45824005454903</v>
+        <v>16.37231143763208</v>
       </c>
       <c r="D88">
-        <v>42.47444005454903</v>
+        <v>42.71021143763208</v>
       </c>
       <c r="E88">
-        <v>19.4962</v>
+        <v>19.8179</v>
       </c>
       <c r="F88">
-        <v>27.6662</v>
+        <v>27.9879</v>
       </c>
       <c r="G88">
         <v>1.65</v>
@@ -8503,28 +8503,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M88">
-        <v>1.52994086</v>
+        <v>1.54773087</v>
       </c>
       <c r="N88">
-        <v>6.664548935918368</v>
+        <v>6.646758925918368</v>
       </c>
       <c r="O88">
-        <v>1.79942821269796</v>
+        <v>1.794624909997959</v>
       </c>
       <c r="P88">
-        <v>4.865120723220409</v>
+        <v>4.852134015920408</v>
       </c>
       <c r="Q88">
-        <v>7.895120723220409</v>
+        <v>7.882134015920409</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3313166586711001</v>
+        <v>0.3521982144478351</v>
       </c>
       <c r="T88">
-        <v>5.229337872870092</v>
+        <v>5.61179090022048</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.356082715457622</v>
+        <v>5.294518546314429</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08090679787821857</v>
+        <v>0.0807119235424831</v>
       </c>
       <c r="C89">
-        <v>16.37231143763208</v>
+        <v>16.28901491811924</v>
       </c>
       <c r="D89">
-        <v>42.71021143763208</v>
+        <v>42.94861491811925</v>
       </c>
       <c r="E89">
-        <v>19.8179</v>
+        <v>20.1396</v>
       </c>
       <c r="F89">
-        <v>27.9879</v>
+        <v>28.3096</v>
       </c>
       <c r="G89">
         <v>1.65</v>
@@ -8585,28 +8585,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M89">
-        <v>1.54773087</v>
+        <v>1.56552088</v>
       </c>
       <c r="N89">
-        <v>6.646758925918368</v>
+        <v>6.628968915918368</v>
       </c>
       <c r="O89">
-        <v>1.794624909997959</v>
+        <v>1.78982160729796</v>
       </c>
       <c r="P89">
-        <v>4.852134015920408</v>
+        <v>4.839147308620409</v>
       </c>
       <c r="Q89">
-        <v>7.882134015920409</v>
+        <v>7.869147308620409</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3521982144478351</v>
+        <v>0.3765600295206926</v>
       </c>
       <c r="T89">
-        <v>5.61179090022048</v>
+        <v>6.057986098795934</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.294518546314429</v>
+        <v>5.234353562833584</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0807119235424831</v>
+        <v>0.08051704920674767</v>
       </c>
       <c r="C90">
-        <v>16.28901491811924</v>
+        <v>16.20839481961325</v>
       </c>
       <c r="D90">
-        <v>42.94861491811925</v>
+        <v>43.18969481961326</v>
       </c>
       <c r="E90">
-        <v>20.1396</v>
+        <v>20.4613</v>
       </c>
       <c r="F90">
-        <v>28.3096</v>
+        <v>28.6313</v>
       </c>
       <c r="G90">
         <v>1.65</v>
@@ -8667,28 +8667,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M90">
-        <v>1.56552088</v>
+        <v>1.58331089</v>
       </c>
       <c r="N90">
-        <v>6.628968915918368</v>
+        <v>6.611178905918369</v>
       </c>
       <c r="O90">
-        <v>1.78982160729796</v>
+        <v>1.78501830459796</v>
       </c>
       <c r="P90">
-        <v>4.839147308620409</v>
+        <v>4.826160601320409</v>
       </c>
       <c r="Q90">
-        <v>7.869147308620409</v>
+        <v>7.856160601320409</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3765600295206926</v>
+        <v>0.405351265515888</v>
       </c>
       <c r="T90">
-        <v>6.057986098795934</v>
+        <v>6.58530769711238</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.234353562833584</v>
+        <v>5.175540601453432</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08051704920674767</v>
+        <v>0.08032217487101223</v>
       </c>
       <c r="C91">
-        <v>16.20839481961325</v>
+        <v>16.13049646652675</v>
       </c>
       <c r="D91">
-        <v>43.18969481961326</v>
+        <v>43.43349646652675</v>
       </c>
       <c r="E91">
-        <v>20.4613</v>
+        <v>20.783</v>
       </c>
       <c r="F91">
-        <v>28.6313</v>
+        <v>28.953</v>
       </c>
       <c r="G91">
         <v>1.65</v>
@@ -8749,28 +8749,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M91">
-        <v>1.58331089</v>
+        <v>1.6011009</v>
       </c>
       <c r="N91">
-        <v>6.611178905918369</v>
+        <v>6.593388895918368</v>
       </c>
       <c r="O91">
-        <v>1.78501830459796</v>
+        <v>1.780215001897959</v>
       </c>
       <c r="P91">
-        <v>4.826160601320409</v>
+        <v>4.813173894020409</v>
       </c>
       <c r="Q91">
-        <v>7.856160601320409</v>
+        <v>7.843173894020409</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.405351265515888</v>
+        <v>0.4399007487101223</v>
       </c>
       <c r="T91">
-        <v>6.58530769711238</v>
+        <v>7.218093615092114</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.175540601453432</v>
+        <v>5.118034594770615</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08032217487101223</v>
+        <v>0.08012730053527678</v>
       </c>
       <c r="C92">
-        <v>16.13049646652675</v>
+        <v>16.05536621248986</v>
       </c>
       <c r="D92">
-        <v>43.43349646652675</v>
+        <v>43.68006621248986</v>
       </c>
       <c r="E92">
-        <v>20.783</v>
+        <v>21.1047</v>
       </c>
       <c r="F92">
-        <v>28.953</v>
+        <v>29.2747</v>
       </c>
       <c r="G92">
         <v>1.65</v>
@@ -8831,28 +8831,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M92">
-        <v>1.6011009</v>
+        <v>1.61889091</v>
       </c>
       <c r="N92">
-        <v>6.593388895918368</v>
+        <v>6.575598885918368</v>
       </c>
       <c r="O92">
-        <v>1.780215001897959</v>
+        <v>1.77541169919796</v>
       </c>
       <c r="P92">
-        <v>4.813173894020409</v>
+        <v>4.800187186720409</v>
       </c>
       <c r="Q92">
-        <v>7.843173894020409</v>
+        <v>7.830187186720409</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4399007487101223</v>
+        <v>0.4821278948364088</v>
       </c>
       <c r="T92">
-        <v>7.218093615092114</v>
+        <v>7.991498625956234</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.118034594770615</v>
+        <v>5.061792456366542</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08012730053527678</v>
+        <v>0.07993242619954133</v>
       </c>
       <c r="C93">
-        <v>16.05536621248986</v>
+        <v>15.98305146973108</v>
       </c>
       <c r="D93">
-        <v>43.68006621248986</v>
+        <v>43.92945146973108</v>
       </c>
       <c r="E93">
-        <v>21.1047</v>
+        <v>21.4264</v>
       </c>
       <c r="F93">
-        <v>29.2747</v>
+        <v>29.5964</v>
       </c>
       <c r="G93">
         <v>1.65</v>
@@ -8913,28 +8913,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M93">
-        <v>1.61889091</v>
+        <v>1.63668092</v>
       </c>
       <c r="N93">
-        <v>6.575598885918368</v>
+        <v>6.557808875918369</v>
       </c>
       <c r="O93">
-        <v>1.77541169919796</v>
+        <v>1.77060839649796</v>
       </c>
       <c r="P93">
-        <v>4.800187186720409</v>
+        <v>4.787200479420409</v>
       </c>
       <c r="Q93">
-        <v>7.830187186720409</v>
+        <v>7.81720047942041</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4821278948364088</v>
+        <v>0.5349118274942668</v>
       </c>
       <c r="T93">
-        <v>7.991498625956234</v>
+        <v>8.958254889536384</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.061792456366542</v>
+        <v>5.006772973145167</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07993242619954133</v>
+        <v>0.07973755186380588</v>
       </c>
       <c r="C94">
-        <v>15.98305146973108</v>
+        <v>15.91360073947044</v>
       </c>
       <c r="D94">
-        <v>43.92945146973108</v>
+        <v>44.18170073947044</v>
       </c>
       <c r="E94">
-        <v>21.4264</v>
+        <v>21.7481</v>
       </c>
       <c r="F94">
-        <v>29.5964</v>
+        <v>29.9181</v>
       </c>
       <c r="G94">
         <v>1.65</v>
@@ -8995,28 +8995,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M94">
-        <v>1.63668092</v>
+        <v>1.65447093</v>
       </c>
       <c r="N94">
-        <v>6.557808875918369</v>
+        <v>6.540018865918368</v>
       </c>
       <c r="O94">
-        <v>1.77060839649796</v>
+        <v>1.765805093797959</v>
       </c>
       <c r="P94">
-        <v>4.787200479420409</v>
+        <v>4.774213772120408</v>
       </c>
       <c r="Q94">
-        <v>7.81720047942041</v>
+        <v>7.804213772120408</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5349118274942668</v>
+        <v>0.6027768837686558</v>
       </c>
       <c r="T94">
-        <v>8.958254889536384</v>
+        <v>10.20122722842515</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.006772973145167</v>
+        <v>4.952936704616724</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07973755186380588</v>
+        <v>0.07954267752807044</v>
       </c>
       <c r="C95">
-        <v>15.91360073947044</v>
+        <v>15.84706364336576</v>
       </c>
       <c r="D95">
-        <v>44.18170073947044</v>
+        <v>44.43686364336577</v>
       </c>
       <c r="E95">
-        <v>21.7481</v>
+        <v>22.0698</v>
       </c>
       <c r="F95">
-        <v>29.9181</v>
+        <v>30.2398</v>
       </c>
       <c r="G95">
         <v>1.65</v>
@@ -9077,28 +9077,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M95">
-        <v>1.65447093</v>
+        <v>1.67226094</v>
       </c>
       <c r="N95">
-        <v>6.540018865918368</v>
+        <v>6.522228855918368</v>
       </c>
       <c r="O95">
-        <v>1.765805093797959</v>
+        <v>1.76100179109796</v>
       </c>
       <c r="P95">
-        <v>4.774213772120408</v>
+        <v>4.761227064820408</v>
       </c>
       <c r="Q95">
-        <v>7.804213772120408</v>
+        <v>7.791227064820409</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6027768837686558</v>
+        <v>0.6932636254678413</v>
       </c>
       <c r="T95">
-        <v>10.20122722842515</v>
+        <v>11.85852368027684</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.952936704616724</v>
+        <v>4.900245888610163</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07954267752807044</v>
+        <v>0.07934780319233499</v>
       </c>
       <c r="C96">
-        <v>15.84706364336576</v>
+        <v>15.78349095605509</v>
       </c>
       <c r="D96">
-        <v>44.43686364336577</v>
+        <v>44.69499095605509</v>
       </c>
       <c r="E96">
-        <v>22.0698</v>
+        <v>22.3915</v>
       </c>
       <c r="F96">
-        <v>30.2398</v>
+        <v>30.5615</v>
       </c>
       <c r="G96">
         <v>1.65</v>
@@ -9159,28 +9159,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M96">
-        <v>1.67226094</v>
+        <v>1.69005095</v>
       </c>
       <c r="N96">
-        <v>6.522228855918368</v>
+        <v>6.504438845918369</v>
       </c>
       <c r="O96">
-        <v>1.76100179109796</v>
+        <v>1.75619848839796</v>
       </c>
       <c r="P96">
-        <v>4.761227064820408</v>
+        <v>4.748240357520409</v>
       </c>
       <c r="Q96">
-        <v>7.791227064820409</v>
+        <v>7.778240357520409</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6932636254678413</v>
+        <v>0.8199450638467009</v>
       </c>
       <c r="T96">
-        <v>11.85852368027684</v>
+        <v>14.1787387128692</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.900245888610163</v>
+        <v>4.848664352940583</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07934780319233499</v>
+        <v>0.07915292885659954</v>
       </c>
       <c r="C97">
-        <v>15.78349095605509</v>
+        <v>15.72293463883962</v>
       </c>
       <c r="D97">
-        <v>44.69499095605509</v>
+        <v>44.95613463883963</v>
       </c>
       <c r="E97">
-        <v>22.3915</v>
+        <v>22.71320000000001</v>
       </c>
       <c r="F97">
-        <v>30.5615</v>
+        <v>30.88320000000001</v>
       </c>
       <c r="G97">
         <v>1.65</v>
@@ -9241,28 +9241,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M97">
-        <v>1.69005095</v>
+        <v>1.70784096</v>
       </c>
       <c r="N97">
-        <v>6.504438845918369</v>
+        <v>6.486648835918368</v>
       </c>
       <c r="O97">
-        <v>1.75619848839796</v>
+        <v>1.751395185697959</v>
       </c>
       <c r="P97">
-        <v>4.748240357520409</v>
+        <v>4.735253650220408</v>
       </c>
       <c r="Q97">
-        <v>7.778240357520409</v>
+        <v>7.765253650220409</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8199450638467009</v>
+        <v>1.00996722141499</v>
       </c>
       <c r="T97">
-        <v>14.1787387128692</v>
+        <v>17.65906126175775</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.848664352940583</v>
+        <v>4.798157432597451</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07915292885659955</v>
+        <v>0.0789580545208641</v>
       </c>
       <c r="C98">
-        <v>15.72293463883961</v>
+        <v>15.66544787455477</v>
       </c>
       <c r="D98">
-        <v>44.95613463883961</v>
+        <v>45.22034787455478</v>
       </c>
       <c r="E98">
-        <v>22.7132</v>
+        <v>23.0349</v>
       </c>
       <c r="F98">
-        <v>30.8832</v>
+        <v>31.2049</v>
       </c>
       <c r="G98">
         <v>1.65</v>
@@ -9323,28 +9323,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M98">
-        <v>1.70784096</v>
+        <v>1.72563097</v>
       </c>
       <c r="N98">
-        <v>6.486648835918368</v>
+        <v>6.468858825918368</v>
       </c>
       <c r="O98">
-        <v>1.751395185697959</v>
+        <v>1.74659188299796</v>
       </c>
       <c r="P98">
-        <v>4.735253650220408</v>
+        <v>4.722266942920409</v>
       </c>
       <c r="Q98">
-        <v>7.765253650220409</v>
+        <v>7.752266942920409</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.009967221414988</v>
+        <v>1.326670817362136</v>
       </c>
       <c r="T98">
-        <v>17.6590612617577</v>
+        <v>23.45959884323859</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.798157432597452</v>
+        <v>4.748691892055211</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0789580545208641</v>
+        <v>0.07876318018512865</v>
       </c>
       <c r="C99">
-        <v>15.66544787455477</v>
+        <v>15.61108510367794</v>
       </c>
       <c r="D99">
-        <v>45.22034787455478</v>
+        <v>45.48768510367794</v>
       </c>
       <c r="E99">
-        <v>23.0349</v>
+        <v>23.3566</v>
       </c>
       <c r="F99">
-        <v>31.2049</v>
+        <v>31.5266</v>
       </c>
       <c r="G99">
         <v>1.65</v>
@@ -9405,28 +9405,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M99">
-        <v>1.72563097</v>
+        <v>1.74342098</v>
       </c>
       <c r="N99">
-        <v>6.468858825918368</v>
+        <v>6.451068815918369</v>
       </c>
       <c r="O99">
-        <v>1.74659188299796</v>
+        <v>1.74178858029796</v>
       </c>
       <c r="P99">
-        <v>4.722266942920409</v>
+        <v>4.709280235620409</v>
       </c>
       <c r="Q99">
-        <v>7.752266942920409</v>
+        <v>7.739280235620409</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.326670817362136</v>
+        <v>1.960078009256431</v>
       </c>
       <c r="T99">
-        <v>23.45959884323859</v>
+        <v>35.06067400620036</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.748691892055211</v>
+        <v>4.700235852340361</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07876318018512865</v>
+        <v>0.07856830584939321</v>
       </c>
       <c r="C100">
-        <v>15.61108510367794</v>
+        <v>15.55990206172465</v>
       </c>
       <c r="D100">
-        <v>45.48768510367794</v>
+        <v>45.75820206172465</v>
       </c>
       <c r="E100">
-        <v>23.3566</v>
+        <v>23.6783</v>
       </c>
       <c r="F100">
-        <v>31.5266</v>
+        <v>31.8483</v>
       </c>
       <c r="G100">
         <v>1.65</v>
@@ -9487,28 +9487,28 @@
         <v>8.194489795918368</v>
       </c>
       <c r="M100">
-        <v>1.74342098</v>
+        <v>1.76121099</v>
       </c>
       <c r="N100">
-        <v>6.451068815918369</v>
+        <v>6.433278805918368</v>
       </c>
       <c r="O100">
-        <v>1.74178858029796</v>
+        <v>1.73698527759796</v>
       </c>
       <c r="P100">
-        <v>4.709280235620409</v>
+        <v>4.696293528320409</v>
       </c>
       <c r="Q100">
-        <v>7.739280235620409</v>
+        <v>7.726293528320409</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.960078009256431</v>
+        <v>3.860299584939317</v>
       </c>
       <c r="T100">
-        <v>35.06067400620036</v>
+        <v>69.86389949508569</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.700235852340361</v>
+        <v>4.652758722518741</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07856830584939321</v>
-      </c>
-      <c r="C101">
-        <v>15.55990206172465</v>
-      </c>
-      <c r="D101">
-        <v>45.75820206172465</v>
-      </c>
-      <c r="E101">
-        <v>23.6783</v>
-      </c>
-      <c r="F101">
-        <v>31.8483</v>
-      </c>
-      <c r="G101">
-        <v>1.65</v>
-      </c>
-      <c r="H101">
-        <v>24</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.22448979591837</v>
-      </c>
-      <c r="K101">
-        <v>3.03</v>
-      </c>
-      <c r="L101">
-        <v>8.194489795918368</v>
-      </c>
-      <c r="M101">
-        <v>1.76121099</v>
-      </c>
-      <c r="N101">
-        <v>6.433278805918368</v>
-      </c>
-      <c r="O101">
-        <v>1.73698527759796</v>
-      </c>
-      <c r="P101">
-        <v>4.696293528320409</v>
-      </c>
-      <c r="Q101">
-        <v>7.726293528320409</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.860299584939317</v>
-      </c>
-      <c r="T101">
-        <v>69.86389949508569</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.040369</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.652758722518741</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
